--- a/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
+++ b/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
@@ -22,7 +22,7 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Auditores!$B$1:$I$30</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Evidências!$B$1:$K$71</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$O$57</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$O$58</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Indústria'!$B$1:$O$56</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$49</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Painel!$B$1:$F$45</definedName>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="341">
   <si>
     <t xml:space="preserve">Técnica de auditoria — Como usar esta planilha</t>
   </si>
@@ -240,10 +240,10 @@
     <t xml:space="preserve">Amostra completa, sem desvio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Desvio isolado: ampliar a amostra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amostra completa, com um desvio. Amplie antes de concluir.</t>
+    <t xml:space="preserve">Desvio pontual: não conformidade, ampliar a amostra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amostra completa, com um desvio. Já é não conformidade; amplie a amostra para saber se é pontual ou repetido.</t>
   </si>
   <si>
     <t xml:space="preserve">Desvio repetido: não conformidade</t>
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Força da evidência</t>
   </si>
   <si>
-    <t xml:space="preserve">Forte: duas fontes ou mais. Média: só observação ou só registro. Fraca: só entrevista. Não conformidade pede evidência forte.</t>
+    <t xml:space="preserve">Forte: duas fontes ou mais. Média: só observação ou só registro. Fraca: só entrevista. Não conformidade pede ao menos uma fonte objetiva (força média ou forte); a que só tem entrevista pede corroboração.</t>
   </si>
   <si>
     <t xml:space="preserve">Nível do auditor</t>
@@ -681,10 +681,10 @@
     <t xml:space="preserve">Amostras sem desvio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Desvio isolado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampliar antes de concluir.</t>
+    <t xml:space="preserve">Desvio pontual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não conformidade; ampliar para medir a extensão.</t>
   </si>
   <si>
     <t xml:space="preserve">Desvio repetido</t>
@@ -720,10 +720,10 @@
     <t xml:space="preserve">Só entrevista.</t>
   </si>
   <si>
-    <t xml:space="preserve">Não conformidades sem corroboração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buscar outra fonte antes do relatório.</t>
+    <t xml:space="preserve">Não conformidades sem evidência objetiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buscar registro ou observação antes do relatório.</t>
   </si>
   <si>
     <t xml:space="preserve">AUDITORES</t>
@@ -786,13 +786,13 @@
     <t xml:space="preserve">O tamanho da amostra e o resultado ficam anotados: quantos se viu e quantos desvios.</t>
   </si>
   <si>
-    <t xml:space="preserve">Um desvio isolado leva a ampliar a amostra antes de concluir.</t>
+    <t xml:space="preserve">Um desvio pontual já é não conformidade, e a amostra é ampliada para medir a extensão.</t>
   </si>
   <si>
     <t xml:space="preserve">Cada constatação tem ao menos uma evidência objetiva: observação ou registro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Toda não conformidade é corroborada por duas fontes.</t>
+    <t xml:space="preserve">Toda não conformidade tem ao menos uma evidência objetiva; a que nasce de entrevista é corroborada.</t>
   </si>
   <si>
     <t xml:space="preserve">O auditor segue ao menos uma trilha até o fim em cada processo.</t>
@@ -843,13 +843,13 @@
     <t xml:space="preserve">Pizzaria (loja com salão e delivery)</t>
   </si>
   <si>
-    <t xml:space="preserve">Atendente do turno do almoço</t>
+    <t xml:space="preserve">Atendente do turno da tarde</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Pizzaiolo do turno do almoço</t>
+    <t xml:space="preserve">Pizzaiolo do turno da tarde</t>
   </si>
   <si>
     <t xml:space="preserve">Observador</t>
@@ -936,6 +936,12 @@
     <t xml:space="preserve">Planilha FR-07: termômetro da câmara verificado em 15/03, reprovado e trocado; leituras anteriores não revistas</t>
   </si>
   <si>
+    <t xml:space="preserve">Como as leituras de temperatura da câmara fria são registradas?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 leituras de fevereiro: 1 sem anotação, a do domingo, 14/02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Como o recebimento confere a temperatura dos refrigerados?</t>
   </si>
   <si>
@@ -1047,7 +1053,7 @@
     <t xml:space="preserve">Ordens de manutenção corretiva, com o produto afetado</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1.3</t>
+    <t xml:space="preserve">8.7</t>
   </si>
   <si>
     <t xml:space="preserve">Quebra do chiller, 22/07: produto afetado sem destino.</t>
@@ -1138,9 +1144,6 @@
   </si>
   <si>
     <t xml:space="preserve">O que se faz com a bobina fora de espessura?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7</t>
   </si>
   <si>
     <t xml:space="preserve">Líder do turno</t>
@@ -1749,7 +1752,7 @@
                   <c:v>Conforme na amostra</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Desvio isolado: ampliar a amostra</c:v>
+                  <c:v>Desvio pontual: não conformidade, ampliar a amostra</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Desvio repetido: não conformidade</c:v>
@@ -1784,11 +1787,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="18486829"/>
-        <c:axId val="84240164"/>
+        <c:axId val="45500717"/>
+        <c:axId val="21500126"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="18486829"/>
+        <c:axId val="45500717"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1820,7 +1823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84240164"/>
+        <c:crossAx val="21500126"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1828,7 +1831,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84240164"/>
+        <c:axId val="21500126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1868,7 +1871,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18486829"/>
+        <c:crossAx val="45500717"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1909,8 +1912,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2346120</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2264,7 +2267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
         <v>33</v>
       </c>
@@ -2288,7 +2291,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
         <v>39</v>
       </c>
@@ -2714,7 +2717,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="5"/>
       <c r="N12" s="17" t="str">
-        <f aca="false">IF(OR(I12="",K12="",L12=""),"",IF(K12&lt;I12,"Amostra incompleta",IF(L12=0,"Conforme na amostra",IF(L12=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I12="",K12="",L12=""),"",IF(K12&lt;I12,"Amostra incompleta",IF(L12=0,"Conforme na amostra",IF(L12=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O12" s="18" t="str">
@@ -2744,7 +2747,7 @@
       <c r="L13" s="14"/>
       <c r="M13" s="5"/>
       <c r="N13" s="17" t="str">
-        <f aca="false">IF(OR(I13="",K13="",L13=""),"",IF(K13&lt;I13,"Amostra incompleta",IF(L13=0,"Conforme na amostra",IF(L13=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I13="",K13="",L13=""),"",IF(K13&lt;I13,"Amostra incompleta",IF(L13=0,"Conforme na amostra",IF(L13=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O13" s="18" t="str">
@@ -2774,7 +2777,7 @@
       <c r="L14" s="14"/>
       <c r="M14" s="5"/>
       <c r="N14" s="17" t="str">
-        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O14" s="18" t="str">
@@ -2804,7 +2807,7 @@
       <c r="L15" s="14"/>
       <c r="M15" s="5"/>
       <c r="N15" s="17" t="str">
-        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O15" s="18" t="str">
@@ -2834,7 +2837,7 @@
       <c r="L16" s="14"/>
       <c r="M16" s="5"/>
       <c r="N16" s="17" t="str">
-        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O16" s="18" t="str">
@@ -2864,7 +2867,7 @@
       <c r="L17" s="14"/>
       <c r="M17" s="5"/>
       <c r="N17" s="17" t="str">
-        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O17" s="18" t="str">
@@ -2894,7 +2897,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="5"/>
       <c r="N18" s="17" t="str">
-        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O18" s="18" t="str">
@@ -2924,7 +2927,7 @@
       <c r="L19" s="14"/>
       <c r="M19" s="5"/>
       <c r="N19" s="17" t="str">
-        <f aca="false">IF(OR(I19="",K19="",L19=""),"",IF(K19&lt;I19,"Amostra incompleta",IF(L19=0,"Conforme na amostra",IF(L19=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I19="",K19="",L19=""),"",IF(K19&lt;I19,"Amostra incompleta",IF(L19=0,"Conforme na amostra",IF(L19=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O19" s="18" t="str">
@@ -2954,7 +2957,7 @@
       <c r="L20" s="14"/>
       <c r="M20" s="5"/>
       <c r="N20" s="17" t="str">
-        <f aca="false">IF(OR(I20="",K20="",L20=""),"",IF(K20&lt;I20,"Amostra incompleta",IF(L20=0,"Conforme na amostra",IF(L20=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I20="",K20="",L20=""),"",IF(K20&lt;I20,"Amostra incompleta",IF(L20=0,"Conforme na amostra",IF(L20=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O20" s="18" t="str">
@@ -2984,7 +2987,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="5"/>
       <c r="N21" s="17" t="str">
-        <f aca="false">IF(OR(I21="",K21="",L21=""),"",IF(K21&lt;I21,"Amostra incompleta",IF(L21=0,"Conforme na amostra",IF(L21=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I21="",K21="",L21=""),"",IF(K21&lt;I21,"Amostra incompleta",IF(L21=0,"Conforme na amostra",IF(L21=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O21" s="18" t="str">
@@ -3014,7 +3017,7 @@
       <c r="L22" s="14"/>
       <c r="M22" s="5"/>
       <c r="N22" s="17" t="str">
-        <f aca="false">IF(OR(I22="",K22="",L22=""),"",IF(K22&lt;I22,"Amostra incompleta",IF(L22=0,"Conforme na amostra",IF(L22=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I22="",K22="",L22=""),"",IF(K22&lt;I22,"Amostra incompleta",IF(L22=0,"Conforme na amostra",IF(L22=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O22" s="18" t="str">
@@ -3044,7 +3047,7 @@
       <c r="L23" s="14"/>
       <c r="M23" s="5"/>
       <c r="N23" s="17" t="str">
-        <f aca="false">IF(OR(I23="",K23="",L23=""),"",IF(K23&lt;I23,"Amostra incompleta",IF(L23=0,"Conforme na amostra",IF(L23=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I23="",K23="",L23=""),"",IF(K23&lt;I23,"Amostra incompleta",IF(L23=0,"Conforme na amostra",IF(L23=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O23" s="18" t="str">
@@ -3074,7 +3077,7 @@
       <c r="L24" s="14"/>
       <c r="M24" s="5"/>
       <c r="N24" s="17" t="str">
-        <f aca="false">IF(OR(I24="",K24="",L24=""),"",IF(K24&lt;I24,"Amostra incompleta",IF(L24=0,"Conforme na amostra",IF(L24=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I24="",K24="",L24=""),"",IF(K24&lt;I24,"Amostra incompleta",IF(L24=0,"Conforme na amostra",IF(L24=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O24" s="18" t="str">
@@ -3104,7 +3107,7 @@
       <c r="L25" s="14"/>
       <c r="M25" s="5"/>
       <c r="N25" s="17" t="str">
-        <f aca="false">IF(OR(I25="",K25="",L25=""),"",IF(K25&lt;I25,"Amostra incompleta",IF(L25=0,"Conforme na amostra",IF(L25=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I25="",K25="",L25=""),"",IF(K25&lt;I25,"Amostra incompleta",IF(L25=0,"Conforme na amostra",IF(L25=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O25" s="18" t="str">
@@ -3134,7 +3137,7 @@
       <c r="L26" s="14"/>
       <c r="M26" s="5"/>
       <c r="N26" s="17" t="str">
-        <f aca="false">IF(OR(I26="",K26="",L26=""),"",IF(K26&lt;I26,"Amostra incompleta",IF(L26=0,"Conforme na amostra",IF(L26=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I26="",K26="",L26=""),"",IF(K26&lt;I26,"Amostra incompleta",IF(L26=0,"Conforme na amostra",IF(L26=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O26" s="18" t="str">
@@ -3164,7 +3167,7 @@
       <c r="L27" s="14"/>
       <c r="M27" s="5"/>
       <c r="N27" s="17" t="str">
-        <f aca="false">IF(OR(I27="",K27="",L27=""),"",IF(K27&lt;I27,"Amostra incompleta",IF(L27=0,"Conforme na amostra",IF(L27=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I27="",K27="",L27=""),"",IF(K27&lt;I27,"Amostra incompleta",IF(L27=0,"Conforme na amostra",IF(L27=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O27" s="18" t="str">
@@ -3194,7 +3197,7 @@
       <c r="L28" s="14"/>
       <c r="M28" s="5"/>
       <c r="N28" s="17" t="str">
-        <f aca="false">IF(OR(I28="",K28="",L28=""),"",IF(K28&lt;I28,"Amostra incompleta",IF(L28=0,"Conforme na amostra",IF(L28=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I28="",K28="",L28=""),"",IF(K28&lt;I28,"Amostra incompleta",IF(L28=0,"Conforme na amostra",IF(L28=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O28" s="18" t="str">
@@ -3224,7 +3227,7 @@
       <c r="L29" s="14"/>
       <c r="M29" s="5"/>
       <c r="N29" s="17" t="str">
-        <f aca="false">IF(OR(I29="",K29="",L29=""),"",IF(K29&lt;I29,"Amostra incompleta",IF(L29=0,"Conforme na amostra",IF(L29=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I29="",K29="",L29=""),"",IF(K29&lt;I29,"Amostra incompleta",IF(L29=0,"Conforme na amostra",IF(L29=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O29" s="18" t="str">
@@ -3254,7 +3257,7 @@
       <c r="L30" s="14"/>
       <c r="M30" s="5"/>
       <c r="N30" s="17" t="str">
-        <f aca="false">IF(OR(I30="",K30="",L30=""),"",IF(K30&lt;I30,"Amostra incompleta",IF(L30=0,"Conforme na amostra",IF(L30=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I30="",K30="",L30=""),"",IF(K30&lt;I30,"Amostra incompleta",IF(L30=0,"Conforme na amostra",IF(L30=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O30" s="18" t="str">
@@ -3284,7 +3287,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="5"/>
       <c r="N31" s="17" t="str">
-        <f aca="false">IF(OR(I31="",K31="",L31=""),"",IF(K31&lt;I31,"Amostra incompleta",IF(L31=0,"Conforme na amostra",IF(L31=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I31="",K31="",L31=""),"",IF(K31&lt;I31,"Amostra incompleta",IF(L31=0,"Conforme na amostra",IF(L31=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O31" s="18" t="str">
@@ -3314,7 +3317,7 @@
       <c r="L32" s="14"/>
       <c r="M32" s="5"/>
       <c r="N32" s="17" t="str">
-        <f aca="false">IF(OR(I32="",K32="",L32=""),"",IF(K32&lt;I32,"Amostra incompleta",IF(L32=0,"Conforme na amostra",IF(L32=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I32="",K32="",L32=""),"",IF(K32&lt;I32,"Amostra incompleta",IF(L32=0,"Conforme na amostra",IF(L32=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O32" s="18" t="str">
@@ -3344,7 +3347,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="5"/>
       <c r="N33" s="17" t="str">
-        <f aca="false">IF(OR(I33="",K33="",L33=""),"",IF(K33&lt;I33,"Amostra incompleta",IF(L33=0,"Conforme na amostra",IF(L33=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I33="",K33="",L33=""),"",IF(K33&lt;I33,"Amostra incompleta",IF(L33=0,"Conforme na amostra",IF(L33=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O33" s="18" t="str">
@@ -3374,7 +3377,7 @@
       <c r="L34" s="14"/>
       <c r="M34" s="5"/>
       <c r="N34" s="17" t="str">
-        <f aca="false">IF(OR(I34="",K34="",L34=""),"",IF(K34&lt;I34,"Amostra incompleta",IF(L34=0,"Conforme na amostra",IF(L34=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I34="",K34="",L34=""),"",IF(K34&lt;I34,"Amostra incompleta",IF(L34=0,"Conforme na amostra",IF(L34=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O34" s="18" t="str">
@@ -3404,7 +3407,7 @@
       <c r="L35" s="14"/>
       <c r="M35" s="5"/>
       <c r="N35" s="17" t="str">
-        <f aca="false">IF(OR(I35="",K35="",L35=""),"",IF(K35&lt;I35,"Amostra incompleta",IF(L35=0,"Conforme na amostra",IF(L35=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I35="",K35="",L35=""),"",IF(K35&lt;I35,"Amostra incompleta",IF(L35=0,"Conforme na amostra",IF(L35=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O35" s="18" t="str">
@@ -3434,7 +3437,7 @@
       <c r="L36" s="14"/>
       <c r="M36" s="5"/>
       <c r="N36" s="17" t="str">
-        <f aca="false">IF(OR(I36="",K36="",L36=""),"",IF(K36&lt;I36,"Amostra incompleta",IF(L36=0,"Conforme na amostra",IF(L36=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I36="",K36="",L36=""),"",IF(K36&lt;I36,"Amostra incompleta",IF(L36=0,"Conforme na amostra",IF(L36=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O36" s="18" t="str">
@@ -3464,7 +3467,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="5"/>
       <c r="N37" s="17" t="str">
-        <f aca="false">IF(OR(I37="",K37="",L37=""),"",IF(K37&lt;I37,"Amostra incompleta",IF(L37=0,"Conforme na amostra",IF(L37=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I37="",K37="",L37=""),"",IF(K37&lt;I37,"Amostra incompleta",IF(L37=0,"Conforme na amostra",IF(L37=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O37" s="18" t="str">
@@ -3494,7 +3497,7 @@
       <c r="L38" s="14"/>
       <c r="M38" s="5"/>
       <c r="N38" s="17" t="str">
-        <f aca="false">IF(OR(I38="",K38="",L38=""),"",IF(K38&lt;I38,"Amostra incompleta",IF(L38=0,"Conforme na amostra",IF(L38=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I38="",K38="",L38=""),"",IF(K38&lt;I38,"Amostra incompleta",IF(L38=0,"Conforme na amostra",IF(L38=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O38" s="18" t="str">
@@ -3524,7 +3527,7 @@
       <c r="L39" s="14"/>
       <c r="M39" s="5"/>
       <c r="N39" s="17" t="str">
-        <f aca="false">IF(OR(I39="",K39="",L39=""),"",IF(K39&lt;I39,"Amostra incompleta",IF(L39=0,"Conforme na amostra",IF(L39=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I39="",K39="",L39=""),"",IF(K39&lt;I39,"Amostra incompleta",IF(L39=0,"Conforme na amostra",IF(L39=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O39" s="18" t="str">
@@ -3554,7 +3557,7 @@
       <c r="L40" s="14"/>
       <c r="M40" s="5"/>
       <c r="N40" s="17" t="str">
-        <f aca="false">IF(OR(I40="",K40="",L40=""),"",IF(K40&lt;I40,"Amostra incompleta",IF(L40=0,"Conforme na amostra",IF(L40=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I40="",K40="",L40=""),"",IF(K40&lt;I40,"Amostra incompleta",IF(L40=0,"Conforme na amostra",IF(L40=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O40" s="18" t="str">
@@ -3584,7 +3587,7 @@
       <c r="L41" s="14"/>
       <c r="M41" s="5"/>
       <c r="N41" s="17" t="str">
-        <f aca="false">IF(OR(I41="",K41="",L41=""),"",IF(K41&lt;I41,"Amostra incompleta",IF(L41=0,"Conforme na amostra",IF(L41=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I41="",K41="",L41=""),"",IF(K41&lt;I41,"Amostra incompleta",IF(L41=0,"Conforme na amostra",IF(L41=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v/>
       </c>
       <c r="O41" s="18" t="str">
@@ -3638,8 +3641,8 @@
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
       <c r="E45" s="21" t="str">
-        <f aca="false">COUNTIF(N12:N41,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N12:N41,"Desvio isolado: ampliar a amostra")&amp;" desvio isolado: ampliar a amostra"&amp;", "&amp;COUNTIF(N12:N41,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N12:N41,"Amostra incompleta")&amp;" amostra incompleta"</f>
-        <v>0 conforme na amostra, 0 desvio isolado: ampliar a amostra, 0 desvio repetido: não conformidade, 0 amostra incompleta</v>
+        <f aca="false">COUNTIF(N12:N41,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N12:N41,"Desvio pontual: não conformidade, ampliar a amostra")&amp;" desvio pontual: não conformidade, ampliar a amostra"&amp;", "&amp;COUNTIF(N12:N41,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N12:N41,"Amostra incompleta")&amp;" amostra incompleta"</f>
+        <v>0 conforme na amostra, 0 desvio pontual: não conformidade, ampliar a amostra, 0 desvio repetido: não conformidade, 0 amostra incompleta</v>
       </c>
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
@@ -3659,7 +3662,7 @@
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
       <c r="E46" s="22" t="str">
-        <f aca="false">IF(COUNTA(C12:C41)=0,"Liste as amostras da auditoria",IF(COUNTIF(N12:N41,"Desvio isolado: ampliar a amostra")&gt;0,"Há desvio isolado: amplie a amostra antes de concluir",IF(COUNTIF(N12:N41,"Amostra incompleta")&gt;0,"Há amostra incompleta: complete ou registre por quê",IF(SUMPRODUCT((O12:O41&lt;&gt;"")*(O12:O41&lt;&gt;"OK"))&gt;0,"Há amostra a completar: veja a coluna Conferência","OK"))))</f>
+        <f aca="false">IF(COUNTA(C12:C41)=0,"Liste as amostras da auditoria",IF(COUNTIF(N12:N41,"Desvio pontual: não conformidade, ampliar a amostra")&gt;0,"Há desvio pontual: amplie a amostra para medir a extensão",IF(COUNTIF(N12:N41,"Amostra incompleta")&gt;0,"Há amostra incompleta: complete ou registre por quê",IF(SUMPRODUCT((O12:O41&lt;&gt;"")*(O12:O41&lt;&gt;"OK"))&gt;0,"Há amostra a completar: veja a coluna Conferência","OK"))))</f>
         <v>Liste as amostras da auditoria</v>
       </c>
       <c r="F46" s="22"/>
@@ -3698,7 +3701,7 @@
       <formula>N12="Conforme na amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>N12="Desvio isolado: ampliar a amostra"</formula>
+      <formula>N12="Desvio pontual: não conformidade, ampliar a amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>N12="Amostra incompleta"</formula>
@@ -3919,7 +3922,7 @@
         <v/>
       </c>
       <c r="K7" s="18" t="str">
-        <f aca="false">IF(AND(C7="",D7="",COUNTA(E7:H7)=0),"",IF(D7="","Falta o requisito",IF(C7="","Falta a pergunta",IF(N(I7)=0,"Falta a evidência",IF(H7="","Falta a constatação",IF(AND(H7="Não conformidade",J7&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C7="",D7="",COUNTA(E7:H7)=0),"",IF(D7="","Falta o requisito",IF(C7="","Falta a pergunta",IF(N(I7)=0,"Falta a evidência",IF(H7="","Falta a constatação",IF(AND(H7="Não conformidade",J7="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -3942,7 +3945,7 @@
         <v/>
       </c>
       <c r="K8" s="18" t="str">
-        <f aca="false">IF(AND(C8="",D8="",COUNTA(E8:H8)=0),"",IF(D8="","Falta o requisito",IF(C8="","Falta a pergunta",IF(N(I8)=0,"Falta a evidência",IF(H8="","Falta a constatação",IF(AND(H8="Não conformidade",J8&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C8="",D8="",COUNTA(E8:H8)=0),"",IF(D8="","Falta o requisito",IF(C8="","Falta a pergunta",IF(N(I8)=0,"Falta a evidência",IF(H8="","Falta a constatação",IF(AND(H8="Não conformidade",J8="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -3965,7 +3968,7 @@
         <v/>
       </c>
       <c r="K9" s="18" t="str">
-        <f aca="false">IF(AND(C9="",D9="",COUNTA(E9:H9)=0),"",IF(D9="","Falta o requisito",IF(C9="","Falta a pergunta",IF(N(I9)=0,"Falta a evidência",IF(H9="","Falta a constatação",IF(AND(H9="Não conformidade",J9&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C9="",D9="",COUNTA(E9:H9)=0),"",IF(D9="","Falta o requisito",IF(C9="","Falta a pergunta",IF(N(I9)=0,"Falta a evidência",IF(H9="","Falta a constatação",IF(AND(H9="Não conformidade",J9="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -3988,7 +3991,7 @@
         <v/>
       </c>
       <c r="K10" s="18" t="str">
-        <f aca="false">IF(AND(C10="",D10="",COUNTA(E10:H10)=0),"",IF(D10="","Falta o requisito",IF(C10="","Falta a pergunta",IF(N(I10)=0,"Falta a evidência",IF(H10="","Falta a constatação",IF(AND(H10="Não conformidade",J10&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C10="",D10="",COUNTA(E10:H10)=0),"",IF(D10="","Falta o requisito",IF(C10="","Falta a pergunta",IF(N(I10)=0,"Falta a evidência",IF(H10="","Falta a constatação",IF(AND(H10="Não conformidade",J10="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4011,7 +4014,7 @@
         <v/>
       </c>
       <c r="K11" s="18" t="str">
-        <f aca="false">IF(AND(C11="",D11="",COUNTA(E11:H11)=0),"",IF(D11="","Falta o requisito",IF(C11="","Falta a pergunta",IF(N(I11)=0,"Falta a evidência",IF(H11="","Falta a constatação",IF(AND(H11="Não conformidade",J11&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C11="",D11="",COUNTA(E11:H11)=0),"",IF(D11="","Falta o requisito",IF(C11="","Falta a pergunta",IF(N(I11)=0,"Falta a evidência",IF(H11="","Falta a constatação",IF(AND(H11="Não conformidade",J11="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4034,7 +4037,7 @@
         <v/>
       </c>
       <c r="K12" s="18" t="str">
-        <f aca="false">IF(AND(C12="",D12="",COUNTA(E12:H12)=0),"",IF(D12="","Falta o requisito",IF(C12="","Falta a pergunta",IF(N(I12)=0,"Falta a evidência",IF(H12="","Falta a constatação",IF(AND(H12="Não conformidade",J12&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C12="",D12="",COUNTA(E12:H12)=0),"",IF(D12="","Falta o requisito",IF(C12="","Falta a pergunta",IF(N(I12)=0,"Falta a evidência",IF(H12="","Falta a constatação",IF(AND(H12="Não conformidade",J12="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4057,7 +4060,7 @@
         <v/>
       </c>
       <c r="K13" s="18" t="str">
-        <f aca="false">IF(AND(C13="",D13="",COUNTA(E13:H13)=0),"",IF(D13="","Falta o requisito",IF(C13="","Falta a pergunta",IF(N(I13)=0,"Falta a evidência",IF(H13="","Falta a constatação",IF(AND(H13="Não conformidade",J13&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C13="",D13="",COUNTA(E13:H13)=0),"",IF(D13="","Falta o requisito",IF(C13="","Falta a pergunta",IF(N(I13)=0,"Falta a evidência",IF(H13="","Falta a constatação",IF(AND(H13="Não conformidade",J13="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4080,7 +4083,7 @@
         <v/>
       </c>
       <c r="K14" s="18" t="str">
-        <f aca="false">IF(AND(C14="",D14="",COUNTA(E14:H14)=0),"",IF(D14="","Falta o requisito",IF(C14="","Falta a pergunta",IF(N(I14)=0,"Falta a evidência",IF(H14="","Falta a constatação",IF(AND(H14="Não conformidade",J14&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C14="",D14="",COUNTA(E14:H14)=0),"",IF(D14="","Falta o requisito",IF(C14="","Falta a pergunta",IF(N(I14)=0,"Falta a evidência",IF(H14="","Falta a constatação",IF(AND(H14="Não conformidade",J14="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4103,7 +4106,7 @@
         <v/>
       </c>
       <c r="K15" s="18" t="str">
-        <f aca="false">IF(AND(C15="",D15="",COUNTA(E15:H15)=0),"",IF(D15="","Falta o requisito",IF(C15="","Falta a pergunta",IF(N(I15)=0,"Falta a evidência",IF(H15="","Falta a constatação",IF(AND(H15="Não conformidade",J15&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C15="",D15="",COUNTA(E15:H15)=0),"",IF(D15="","Falta o requisito",IF(C15="","Falta a pergunta",IF(N(I15)=0,"Falta a evidência",IF(H15="","Falta a constatação",IF(AND(H15="Não conformidade",J15="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4126,7 +4129,7 @@
         <v/>
       </c>
       <c r="K16" s="18" t="str">
-        <f aca="false">IF(AND(C16="",D16="",COUNTA(E16:H16)=0),"",IF(D16="","Falta o requisito",IF(C16="","Falta a pergunta",IF(N(I16)=0,"Falta a evidência",IF(H16="","Falta a constatação",IF(AND(H16="Não conformidade",J16&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C16="",D16="",COUNTA(E16:H16)=0),"",IF(D16="","Falta o requisito",IF(C16="","Falta a pergunta",IF(N(I16)=0,"Falta a evidência",IF(H16="","Falta a constatação",IF(AND(H16="Não conformidade",J16="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4149,7 +4152,7 @@
         <v/>
       </c>
       <c r="K17" s="18" t="str">
-        <f aca="false">IF(AND(C17="",D17="",COUNTA(E17:H17)=0),"",IF(D17="","Falta o requisito",IF(C17="","Falta a pergunta",IF(N(I17)=0,"Falta a evidência",IF(H17="","Falta a constatação",IF(AND(H17="Não conformidade",J17&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C17="",D17="",COUNTA(E17:H17)=0),"",IF(D17="","Falta o requisito",IF(C17="","Falta a pergunta",IF(N(I17)=0,"Falta a evidência",IF(H17="","Falta a constatação",IF(AND(H17="Não conformidade",J17="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4172,7 +4175,7 @@
         <v/>
       </c>
       <c r="K18" s="18" t="str">
-        <f aca="false">IF(AND(C18="",D18="",COUNTA(E18:H18)=0),"",IF(D18="","Falta o requisito",IF(C18="","Falta a pergunta",IF(N(I18)=0,"Falta a evidência",IF(H18="","Falta a constatação",IF(AND(H18="Não conformidade",J18&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C18="",D18="",COUNTA(E18:H18)=0),"",IF(D18="","Falta o requisito",IF(C18="","Falta a pergunta",IF(N(I18)=0,"Falta a evidência",IF(H18="","Falta a constatação",IF(AND(H18="Não conformidade",J18="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4195,7 +4198,7 @@
         <v/>
       </c>
       <c r="K19" s="18" t="str">
-        <f aca="false">IF(AND(C19="",D19="",COUNTA(E19:H19)=0),"",IF(D19="","Falta o requisito",IF(C19="","Falta a pergunta",IF(N(I19)=0,"Falta a evidência",IF(H19="","Falta a constatação",IF(AND(H19="Não conformidade",J19&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C19="",D19="",COUNTA(E19:H19)=0),"",IF(D19="","Falta o requisito",IF(C19="","Falta a pergunta",IF(N(I19)=0,"Falta a evidência",IF(H19="","Falta a constatação",IF(AND(H19="Não conformidade",J19="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4218,7 +4221,7 @@
         <v/>
       </c>
       <c r="K20" s="18" t="str">
-        <f aca="false">IF(AND(C20="",D20="",COUNTA(E20:H20)=0),"",IF(D20="","Falta o requisito",IF(C20="","Falta a pergunta",IF(N(I20)=0,"Falta a evidência",IF(H20="","Falta a constatação",IF(AND(H20="Não conformidade",J20&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C20="",D20="",COUNTA(E20:H20)=0),"",IF(D20="","Falta o requisito",IF(C20="","Falta a pergunta",IF(N(I20)=0,"Falta a evidência",IF(H20="","Falta a constatação",IF(AND(H20="Não conformidade",J20="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4241,7 +4244,7 @@
         <v/>
       </c>
       <c r="K21" s="18" t="str">
-        <f aca="false">IF(AND(C21="",D21="",COUNTA(E21:H21)=0),"",IF(D21="","Falta o requisito",IF(C21="","Falta a pergunta",IF(N(I21)=0,"Falta a evidência",IF(H21="","Falta a constatação",IF(AND(H21="Não conformidade",J21&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C21="",D21="",COUNTA(E21:H21)=0),"",IF(D21="","Falta o requisito",IF(C21="","Falta a pergunta",IF(N(I21)=0,"Falta a evidência",IF(H21="","Falta a constatação",IF(AND(H21="Não conformidade",J21="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4264,7 +4267,7 @@
         <v/>
       </c>
       <c r="K22" s="18" t="str">
-        <f aca="false">IF(AND(C22="",D22="",COUNTA(E22:H22)=0),"",IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(N(I22)=0,"Falta a evidência",IF(H22="","Falta a constatação",IF(AND(H22="Não conformidade",J22&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C22="",D22="",COUNTA(E22:H22)=0),"",IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(N(I22)=0,"Falta a evidência",IF(H22="","Falta a constatação",IF(AND(H22="Não conformidade",J22="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4287,7 +4290,7 @@
         <v/>
       </c>
       <c r="K23" s="18" t="str">
-        <f aca="false">IF(AND(C23="",D23="",COUNTA(E23:H23)=0),"",IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(N(I23)=0,"Falta a evidência",IF(H23="","Falta a constatação",IF(AND(H23="Não conformidade",J23&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C23="",D23="",COUNTA(E23:H23)=0),"",IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(N(I23)=0,"Falta a evidência",IF(H23="","Falta a constatação",IF(AND(H23="Não conformidade",J23="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4310,7 +4313,7 @@
         <v/>
       </c>
       <c r="K24" s="18" t="str">
-        <f aca="false">IF(AND(C24="",D24="",COUNTA(E24:H24)=0),"",IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(N(I24)=0,"Falta a evidência",IF(H24="","Falta a constatação",IF(AND(H24="Não conformidade",J24&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C24="",D24="",COUNTA(E24:H24)=0),"",IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(N(I24)=0,"Falta a evidência",IF(H24="","Falta a constatação",IF(AND(H24="Não conformidade",J24="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4333,7 +4336,7 @@
         <v/>
       </c>
       <c r="K25" s="18" t="str">
-        <f aca="false">IF(AND(C25="",D25="",COUNTA(E25:H25)=0),"",IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(N(I25)=0,"Falta a evidência",IF(H25="","Falta a constatação",IF(AND(H25="Não conformidade",J25&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C25="",D25="",COUNTA(E25:H25)=0),"",IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(N(I25)=0,"Falta a evidência",IF(H25="","Falta a constatação",IF(AND(H25="Não conformidade",J25="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4356,7 +4359,7 @@
         <v/>
       </c>
       <c r="K26" s="18" t="str">
-        <f aca="false">IF(AND(C26="",D26="",COUNTA(E26:H26)=0),"",IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(N(I26)=0,"Falta a evidência",IF(H26="","Falta a constatação",IF(AND(H26="Não conformidade",J26&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C26="",D26="",COUNTA(E26:H26)=0),"",IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(N(I26)=0,"Falta a evidência",IF(H26="","Falta a constatação",IF(AND(H26="Não conformidade",J26="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4379,7 +4382,7 @@
         <v/>
       </c>
       <c r="K27" s="18" t="str">
-        <f aca="false">IF(AND(C27="",D27="",COUNTA(E27:H27)=0),"",IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(N(I27)=0,"Falta a evidência",IF(H27="","Falta a constatação",IF(AND(H27="Não conformidade",J27&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C27="",D27="",COUNTA(E27:H27)=0),"",IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(N(I27)=0,"Falta a evidência",IF(H27="","Falta a constatação",IF(AND(H27="Não conformidade",J27="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4402,7 +4405,7 @@
         <v/>
       </c>
       <c r="K28" s="18" t="str">
-        <f aca="false">IF(AND(C28="",D28="",COUNTA(E28:H28)=0),"",IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(N(I28)=0,"Falta a evidência",IF(H28="","Falta a constatação",IF(AND(H28="Não conformidade",J28&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C28="",D28="",COUNTA(E28:H28)=0),"",IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(N(I28)=0,"Falta a evidência",IF(H28="","Falta a constatação",IF(AND(H28="Não conformidade",J28="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4425,7 +4428,7 @@
         <v/>
       </c>
       <c r="K29" s="18" t="str">
-        <f aca="false">IF(AND(C29="",D29="",COUNTA(E29:H29)=0),"",IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(N(I29)=0,"Falta a evidência",IF(H29="","Falta a constatação",IF(AND(H29="Não conformidade",J29&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C29="",D29="",COUNTA(E29:H29)=0),"",IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(N(I29)=0,"Falta a evidência",IF(H29="","Falta a constatação",IF(AND(H29="Não conformidade",J29="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4448,7 +4451,7 @@
         <v/>
       </c>
       <c r="K30" s="18" t="str">
-        <f aca="false">IF(AND(C30="",D30="",COUNTA(E30:H30)=0),"",IF(D30="","Falta o requisito",IF(C30="","Falta a pergunta",IF(N(I30)=0,"Falta a evidência",IF(H30="","Falta a constatação",IF(AND(H30="Não conformidade",J30&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C30="",D30="",COUNTA(E30:H30)=0),"",IF(D30="","Falta o requisito",IF(C30="","Falta a pergunta",IF(N(I30)=0,"Falta a evidência",IF(H30="","Falta a constatação",IF(AND(H30="Não conformidade",J30="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4471,7 +4474,7 @@
         <v/>
       </c>
       <c r="K31" s="18" t="str">
-        <f aca="false">IF(AND(C31="",D31="",COUNTA(E31:H31)=0),"",IF(D31="","Falta o requisito",IF(C31="","Falta a pergunta",IF(N(I31)=0,"Falta a evidência",IF(H31="","Falta a constatação",IF(AND(H31="Não conformidade",J31&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C31="",D31="",COUNTA(E31:H31)=0),"",IF(D31="","Falta o requisito",IF(C31="","Falta a pergunta",IF(N(I31)=0,"Falta a evidência",IF(H31="","Falta a constatação",IF(AND(H31="Não conformidade",J31="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4494,7 +4497,7 @@
         <v/>
       </c>
       <c r="K32" s="18" t="str">
-        <f aca="false">IF(AND(C32="",D32="",COUNTA(E32:H32)=0),"",IF(D32="","Falta o requisito",IF(C32="","Falta a pergunta",IF(N(I32)=0,"Falta a evidência",IF(H32="","Falta a constatação",IF(AND(H32="Não conformidade",J32&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C32="",D32="",COUNTA(E32:H32)=0),"",IF(D32="","Falta o requisito",IF(C32="","Falta a pergunta",IF(N(I32)=0,"Falta a evidência",IF(H32="","Falta a constatação",IF(AND(H32="Não conformidade",J32="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4517,7 +4520,7 @@
         <v/>
       </c>
       <c r="K33" s="18" t="str">
-        <f aca="false">IF(AND(C33="",D33="",COUNTA(E33:H33)=0),"",IF(D33="","Falta o requisito",IF(C33="","Falta a pergunta",IF(N(I33)=0,"Falta a evidência",IF(H33="","Falta a constatação",IF(AND(H33="Não conformidade",J33&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C33="",D33="",COUNTA(E33:H33)=0),"",IF(D33="","Falta o requisito",IF(C33="","Falta a pergunta",IF(N(I33)=0,"Falta a evidência",IF(H33="","Falta a constatação",IF(AND(H33="Não conformidade",J33="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4540,7 +4543,7 @@
         <v/>
       </c>
       <c r="K34" s="18" t="str">
-        <f aca="false">IF(AND(C34="",D34="",COUNTA(E34:H34)=0),"",IF(D34="","Falta o requisito",IF(C34="","Falta a pergunta",IF(N(I34)=0,"Falta a evidência",IF(H34="","Falta a constatação",IF(AND(H34="Não conformidade",J34&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C34="",D34="",COUNTA(E34:H34)=0),"",IF(D34="","Falta o requisito",IF(C34="","Falta a pergunta",IF(N(I34)=0,"Falta a evidência",IF(H34="","Falta a constatação",IF(AND(H34="Não conformidade",J34="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4563,7 +4566,7 @@
         <v/>
       </c>
       <c r="K35" s="18" t="str">
-        <f aca="false">IF(AND(C35="",D35="",COUNTA(E35:H35)=0),"",IF(D35="","Falta o requisito",IF(C35="","Falta a pergunta",IF(N(I35)=0,"Falta a evidência",IF(H35="","Falta a constatação",IF(AND(H35="Não conformidade",J35&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C35="",D35="",COUNTA(E35:H35)=0),"",IF(D35="","Falta o requisito",IF(C35="","Falta a pergunta",IF(N(I35)=0,"Falta a evidência",IF(H35="","Falta a constatação",IF(AND(H35="Não conformidade",J35="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4586,7 +4589,7 @@
         <v/>
       </c>
       <c r="K36" s="18" t="str">
-        <f aca="false">IF(AND(C36="",D36="",COUNTA(E36:H36)=0),"",IF(D36="","Falta o requisito",IF(C36="","Falta a pergunta",IF(N(I36)=0,"Falta a evidência",IF(H36="","Falta a constatação",IF(AND(H36="Não conformidade",J36&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C36="",D36="",COUNTA(E36:H36)=0),"",IF(D36="","Falta o requisito",IF(C36="","Falta a pergunta",IF(N(I36)=0,"Falta a evidência",IF(H36="","Falta a constatação",IF(AND(H36="Não conformidade",J36="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4609,7 +4612,7 @@
         <v/>
       </c>
       <c r="K37" s="18" t="str">
-        <f aca="false">IF(AND(C37="",D37="",COUNTA(E37:H37)=0),"",IF(D37="","Falta o requisito",IF(C37="","Falta a pergunta",IF(N(I37)=0,"Falta a evidência",IF(H37="","Falta a constatação",IF(AND(H37="Não conformidade",J37&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C37="",D37="",COUNTA(E37:H37)=0),"",IF(D37="","Falta o requisito",IF(C37="","Falta a pergunta",IF(N(I37)=0,"Falta a evidência",IF(H37="","Falta a constatação",IF(AND(H37="Não conformidade",J37="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4632,7 +4635,7 @@
         <v/>
       </c>
       <c r="K38" s="18" t="str">
-        <f aca="false">IF(AND(C38="",D38="",COUNTA(E38:H38)=0),"",IF(D38="","Falta o requisito",IF(C38="","Falta a pergunta",IF(N(I38)=0,"Falta a evidência",IF(H38="","Falta a constatação",IF(AND(H38="Não conformidade",J38&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C38="",D38="",COUNTA(E38:H38)=0),"",IF(D38="","Falta o requisito",IF(C38="","Falta a pergunta",IF(N(I38)=0,"Falta a evidência",IF(H38="","Falta a constatação",IF(AND(H38="Não conformidade",J38="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4655,7 +4658,7 @@
         <v/>
       </c>
       <c r="K39" s="18" t="str">
-        <f aca="false">IF(AND(C39="",D39="",COUNTA(E39:H39)=0),"",IF(D39="","Falta o requisito",IF(C39="","Falta a pergunta",IF(N(I39)=0,"Falta a evidência",IF(H39="","Falta a constatação",IF(AND(H39="Não conformidade",J39&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C39="",D39="",COUNTA(E39:H39)=0),"",IF(D39="","Falta o requisito",IF(C39="","Falta a pergunta",IF(N(I39)=0,"Falta a evidência",IF(H39="","Falta a constatação",IF(AND(H39="Não conformidade",J39="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4678,7 +4681,7 @@
         <v/>
       </c>
       <c r="K40" s="18" t="str">
-        <f aca="false">IF(AND(C40="",D40="",COUNTA(E40:H40)=0),"",IF(D40="","Falta o requisito",IF(C40="","Falta a pergunta",IF(N(I40)=0,"Falta a evidência",IF(H40="","Falta a constatação",IF(AND(H40="Não conformidade",J40&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C40="",D40="",COUNTA(E40:H40)=0),"",IF(D40="","Falta o requisito",IF(C40="","Falta a pergunta",IF(N(I40)=0,"Falta a evidência",IF(H40="","Falta a constatação",IF(AND(H40="Não conformidade",J40="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4701,7 +4704,7 @@
         <v/>
       </c>
       <c r="K41" s="18" t="str">
-        <f aca="false">IF(AND(C41="",D41="",COUNTA(E41:H41)=0),"",IF(D41="","Falta o requisito",IF(C41="","Falta a pergunta",IF(N(I41)=0,"Falta a evidência",IF(H41="","Falta a constatação",IF(AND(H41="Não conformidade",J41&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C41="",D41="",COUNTA(E41:H41)=0),"",IF(D41="","Falta o requisito",IF(C41="","Falta a pergunta",IF(N(I41)=0,"Falta a evidência",IF(H41="","Falta a constatação",IF(AND(H41="Não conformidade",J41="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4724,7 +4727,7 @@
         <v/>
       </c>
       <c r="K42" s="18" t="str">
-        <f aca="false">IF(AND(C42="",D42="",COUNTA(E42:H42)=0),"",IF(D42="","Falta o requisito",IF(C42="","Falta a pergunta",IF(N(I42)=0,"Falta a evidência",IF(H42="","Falta a constatação",IF(AND(H42="Não conformidade",J42&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C42="",D42="",COUNTA(E42:H42)=0),"",IF(D42="","Falta o requisito",IF(C42="","Falta a pergunta",IF(N(I42)=0,"Falta a evidência",IF(H42="","Falta a constatação",IF(AND(H42="Não conformidade",J42="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4747,7 +4750,7 @@
         <v/>
       </c>
       <c r="K43" s="18" t="str">
-        <f aca="false">IF(AND(C43="",D43="",COUNTA(E43:H43)=0),"",IF(D43="","Falta o requisito",IF(C43="","Falta a pergunta",IF(N(I43)=0,"Falta a evidência",IF(H43="","Falta a constatação",IF(AND(H43="Não conformidade",J43&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C43="",D43="",COUNTA(E43:H43)=0),"",IF(D43="","Falta o requisito",IF(C43="","Falta a pergunta",IF(N(I43)=0,"Falta a evidência",IF(H43="","Falta a constatação",IF(AND(H43="Não conformidade",J43="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4770,7 +4773,7 @@
         <v/>
       </c>
       <c r="K44" s="18" t="str">
-        <f aca="false">IF(AND(C44="",D44="",COUNTA(E44:H44)=0),"",IF(D44="","Falta o requisito",IF(C44="","Falta a pergunta",IF(N(I44)=0,"Falta a evidência",IF(H44="","Falta a constatação",IF(AND(H44="Não conformidade",J44&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C44="",D44="",COUNTA(E44:H44)=0),"",IF(D44="","Falta o requisito",IF(C44="","Falta a pergunta",IF(N(I44)=0,"Falta a evidência",IF(H44="","Falta a constatação",IF(AND(H44="Não conformidade",J44="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4793,7 +4796,7 @@
         <v/>
       </c>
       <c r="K45" s="18" t="str">
-        <f aca="false">IF(AND(C45="",D45="",COUNTA(E45:H45)=0),"",IF(D45="","Falta o requisito",IF(C45="","Falta a pergunta",IF(N(I45)=0,"Falta a evidência",IF(H45="","Falta a constatação",IF(AND(H45="Não conformidade",J45&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C45="",D45="",COUNTA(E45:H45)=0),"",IF(D45="","Falta o requisito",IF(C45="","Falta a pergunta",IF(N(I45)=0,"Falta a evidência",IF(H45="","Falta a constatação",IF(AND(H45="Não conformidade",J45="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4816,7 +4819,7 @@
         <v/>
       </c>
       <c r="K46" s="18" t="str">
-        <f aca="false">IF(AND(C46="",D46="",COUNTA(E46:H46)=0),"",IF(D46="","Falta o requisito",IF(C46="","Falta a pergunta",IF(N(I46)=0,"Falta a evidência",IF(H46="","Falta a constatação",IF(AND(H46="Não conformidade",J46&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C46="",D46="",COUNTA(E46:H46)=0),"",IF(D46="","Falta o requisito",IF(C46="","Falta a pergunta",IF(N(I46)=0,"Falta a evidência",IF(H46="","Falta a constatação",IF(AND(H46="Não conformidade",J46="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4839,7 +4842,7 @@
         <v/>
       </c>
       <c r="K47" s="18" t="str">
-        <f aca="false">IF(AND(C47="",D47="",COUNTA(E47:H47)=0),"",IF(D47="","Falta o requisito",IF(C47="","Falta a pergunta",IF(N(I47)=0,"Falta a evidência",IF(H47="","Falta a constatação",IF(AND(H47="Não conformidade",J47&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C47="",D47="",COUNTA(E47:H47)=0),"",IF(D47="","Falta o requisito",IF(C47="","Falta a pergunta",IF(N(I47)=0,"Falta a evidência",IF(H47="","Falta a constatação",IF(AND(H47="Não conformidade",J47="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4862,7 +4865,7 @@
         <v/>
       </c>
       <c r="K48" s="18" t="str">
-        <f aca="false">IF(AND(C48="",D48="",COUNTA(E48:H48)=0),"",IF(D48="","Falta o requisito",IF(C48="","Falta a pergunta",IF(N(I48)=0,"Falta a evidência",IF(H48="","Falta a constatação",IF(AND(H48="Não conformidade",J48&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C48="",D48="",COUNTA(E48:H48)=0),"",IF(D48="","Falta o requisito",IF(C48="","Falta a pergunta",IF(N(I48)=0,"Falta a evidência",IF(H48="","Falta a constatação",IF(AND(H48="Não conformidade",J48="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4885,7 +4888,7 @@
         <v/>
       </c>
       <c r="K49" s="18" t="str">
-        <f aca="false">IF(AND(C49="",D49="",COUNTA(E49:H49)=0),"",IF(D49="","Falta o requisito",IF(C49="","Falta a pergunta",IF(N(I49)=0,"Falta a evidência",IF(H49="","Falta a constatação",IF(AND(H49="Não conformidade",J49&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C49="",D49="",COUNTA(E49:H49)=0),"",IF(D49="","Falta o requisito",IF(C49="","Falta a pergunta",IF(N(I49)=0,"Falta a evidência",IF(H49="","Falta a constatação",IF(AND(H49="Não conformidade",J49="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4908,7 +4911,7 @@
         <v/>
       </c>
       <c r="K50" s="18" t="str">
-        <f aca="false">IF(AND(C50="",D50="",COUNTA(E50:H50)=0),"",IF(D50="","Falta o requisito",IF(C50="","Falta a pergunta",IF(N(I50)=0,"Falta a evidência",IF(H50="","Falta a constatação",IF(AND(H50="Não conformidade",J50&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C50="",D50="",COUNTA(E50:H50)=0),"",IF(D50="","Falta o requisito",IF(C50="","Falta a pergunta",IF(N(I50)=0,"Falta a evidência",IF(H50="","Falta a constatação",IF(AND(H50="Não conformidade",J50="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4931,7 +4934,7 @@
         <v/>
       </c>
       <c r="K51" s="18" t="str">
-        <f aca="false">IF(AND(C51="",D51="",COUNTA(E51:H51)=0),"",IF(D51="","Falta o requisito",IF(C51="","Falta a pergunta",IF(N(I51)=0,"Falta a evidência",IF(H51="","Falta a constatação",IF(AND(H51="Não conformidade",J51&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C51="",D51="",COUNTA(E51:H51)=0),"",IF(D51="","Falta o requisito",IF(C51="","Falta a pergunta",IF(N(I51)=0,"Falta a evidência",IF(H51="","Falta a constatação",IF(AND(H51="Não conformidade",J51="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4954,7 +4957,7 @@
         <v/>
       </c>
       <c r="K52" s="18" t="str">
-        <f aca="false">IF(AND(C52="",D52="",COUNTA(E52:H52)=0),"",IF(D52="","Falta o requisito",IF(C52="","Falta a pergunta",IF(N(I52)=0,"Falta a evidência",IF(H52="","Falta a constatação",IF(AND(H52="Não conformidade",J52&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C52="",D52="",COUNTA(E52:H52)=0),"",IF(D52="","Falta o requisito",IF(C52="","Falta a pergunta",IF(N(I52)=0,"Falta a evidência",IF(H52="","Falta a constatação",IF(AND(H52="Não conformidade",J52="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -4977,7 +4980,7 @@
         <v/>
       </c>
       <c r="K53" s="18" t="str">
-        <f aca="false">IF(AND(C53="",D53="",COUNTA(E53:H53)=0),"",IF(D53="","Falta o requisito",IF(C53="","Falta a pergunta",IF(N(I53)=0,"Falta a evidência",IF(H53="","Falta a constatação",IF(AND(H53="Não conformidade",J53&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C53="",D53="",COUNTA(E53:H53)=0),"",IF(D53="","Falta o requisito",IF(C53="","Falta a pergunta",IF(N(I53)=0,"Falta a evidência",IF(H53="","Falta a constatação",IF(AND(H53="Não conformidade",J53="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5000,7 +5003,7 @@
         <v/>
       </c>
       <c r="K54" s="18" t="str">
-        <f aca="false">IF(AND(C54="",D54="",COUNTA(E54:H54)=0),"",IF(D54="","Falta o requisito",IF(C54="","Falta a pergunta",IF(N(I54)=0,"Falta a evidência",IF(H54="","Falta a constatação",IF(AND(H54="Não conformidade",J54&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C54="",D54="",COUNTA(E54:H54)=0),"",IF(D54="","Falta o requisito",IF(C54="","Falta a pergunta",IF(N(I54)=0,"Falta a evidência",IF(H54="","Falta a constatação",IF(AND(H54="Não conformidade",J54="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5023,7 +5026,7 @@
         <v/>
       </c>
       <c r="K55" s="18" t="str">
-        <f aca="false">IF(AND(C55="",D55="",COUNTA(E55:H55)=0),"",IF(D55="","Falta o requisito",IF(C55="","Falta a pergunta",IF(N(I55)=0,"Falta a evidência",IF(H55="","Falta a constatação",IF(AND(H55="Não conformidade",J55&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C55="",D55="",COUNTA(E55:H55)=0),"",IF(D55="","Falta o requisito",IF(C55="","Falta a pergunta",IF(N(I55)=0,"Falta a evidência",IF(H55="","Falta a constatação",IF(AND(H55="Não conformidade",J55="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5046,7 +5049,7 @@
         <v/>
       </c>
       <c r="K56" s="18" t="str">
-        <f aca="false">IF(AND(C56="",D56="",COUNTA(E56:H56)=0),"",IF(D56="","Falta o requisito",IF(C56="","Falta a pergunta",IF(N(I56)=0,"Falta a evidência",IF(H56="","Falta a constatação",IF(AND(H56="Não conformidade",J56&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C56="",D56="",COUNTA(E56:H56)=0),"",IF(D56="","Falta o requisito",IF(C56="","Falta a pergunta",IF(N(I56)=0,"Falta a evidência",IF(H56="","Falta a constatação",IF(AND(H56="Não conformidade",J56="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5069,7 +5072,7 @@
         <v/>
       </c>
       <c r="K57" s="18" t="str">
-        <f aca="false">IF(AND(C57="",D57="",COUNTA(E57:H57)=0),"",IF(D57="","Falta o requisito",IF(C57="","Falta a pergunta",IF(N(I57)=0,"Falta a evidência",IF(H57="","Falta a constatação",IF(AND(H57="Não conformidade",J57&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C57="",D57="",COUNTA(E57:H57)=0),"",IF(D57="","Falta o requisito",IF(C57="","Falta a pergunta",IF(N(I57)=0,"Falta a evidência",IF(H57="","Falta a constatação",IF(AND(H57="Não conformidade",J57="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5092,7 +5095,7 @@
         <v/>
       </c>
       <c r="K58" s="18" t="str">
-        <f aca="false">IF(AND(C58="",D58="",COUNTA(E58:H58)=0),"",IF(D58="","Falta o requisito",IF(C58="","Falta a pergunta",IF(N(I58)=0,"Falta a evidência",IF(H58="","Falta a constatação",IF(AND(H58="Não conformidade",J58&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C58="",D58="",COUNTA(E58:H58)=0),"",IF(D58="","Falta o requisito",IF(C58="","Falta a pergunta",IF(N(I58)=0,"Falta a evidência",IF(H58="","Falta a constatação",IF(AND(H58="Não conformidade",J58="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5115,7 +5118,7 @@
         <v/>
       </c>
       <c r="K59" s="18" t="str">
-        <f aca="false">IF(AND(C59="",D59="",COUNTA(E59:H59)=0),"",IF(D59="","Falta o requisito",IF(C59="","Falta a pergunta",IF(N(I59)=0,"Falta a evidência",IF(H59="","Falta a constatação",IF(AND(H59="Não conformidade",J59&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C59="",D59="",COUNTA(E59:H59)=0),"",IF(D59="","Falta o requisito",IF(C59="","Falta a pergunta",IF(N(I59)=0,"Falta a evidência",IF(H59="","Falta a constatação",IF(AND(H59="Não conformidade",J59="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +5141,7 @@
         <v/>
       </c>
       <c r="K60" s="18" t="str">
-        <f aca="false">IF(AND(C60="",D60="",COUNTA(E60:H60)=0),"",IF(D60="","Falta o requisito",IF(C60="","Falta a pergunta",IF(N(I60)=0,"Falta a evidência",IF(H60="","Falta a constatação",IF(AND(H60="Não conformidade",J60&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C60="",D60="",COUNTA(E60:H60)=0),"",IF(D60="","Falta o requisito",IF(C60="","Falta a pergunta",IF(N(I60)=0,"Falta a evidência",IF(H60="","Falta a constatação",IF(AND(H60="Não conformidade",J60="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5161,7 +5164,7 @@
         <v/>
       </c>
       <c r="K61" s="18" t="str">
-        <f aca="false">IF(AND(C61="",D61="",COUNTA(E61:H61)=0),"",IF(D61="","Falta o requisito",IF(C61="","Falta a pergunta",IF(N(I61)=0,"Falta a evidência",IF(H61="","Falta a constatação",IF(AND(H61="Não conformidade",J61&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C61="",D61="",COUNTA(E61:H61)=0),"",IF(D61="","Falta o requisito",IF(C61="","Falta a pergunta",IF(N(I61)=0,"Falta a evidência",IF(H61="","Falta a constatação",IF(AND(H61="Não conformidade",J61="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5187,7 @@
         <v/>
       </c>
       <c r="K62" s="18" t="str">
-        <f aca="false">IF(AND(C62="",D62="",COUNTA(E62:H62)=0),"",IF(D62="","Falta o requisito",IF(C62="","Falta a pergunta",IF(N(I62)=0,"Falta a evidência",IF(H62="","Falta a constatação",IF(AND(H62="Não conformidade",J62&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C62="",D62="",COUNTA(E62:H62)=0),"",IF(D62="","Falta o requisito",IF(C62="","Falta a pergunta",IF(N(I62)=0,"Falta a evidência",IF(H62="","Falta a constatação",IF(AND(H62="Não conformidade",J62="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5207,7 +5210,7 @@
         <v/>
       </c>
       <c r="K63" s="18" t="str">
-        <f aca="false">IF(AND(C63="",D63="",COUNTA(E63:H63)=0),"",IF(D63="","Falta o requisito",IF(C63="","Falta a pergunta",IF(N(I63)=0,"Falta a evidência",IF(H63="","Falta a constatação",IF(AND(H63="Não conformidade",J63&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C63="",D63="",COUNTA(E63:H63)=0),"",IF(D63="","Falta o requisito",IF(C63="","Falta a pergunta",IF(N(I63)=0,"Falta a evidência",IF(H63="","Falta a constatação",IF(AND(H63="Não conformidade",J63="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5230,7 +5233,7 @@
         <v/>
       </c>
       <c r="K64" s="18" t="str">
-        <f aca="false">IF(AND(C64="",D64="",COUNTA(E64:H64)=0),"",IF(D64="","Falta o requisito",IF(C64="","Falta a pergunta",IF(N(I64)=0,"Falta a evidência",IF(H64="","Falta a constatação",IF(AND(H64="Não conformidade",J64&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C64="",D64="",COUNTA(E64:H64)=0),"",IF(D64="","Falta o requisito",IF(C64="","Falta a pergunta",IF(N(I64)=0,"Falta a evidência",IF(H64="","Falta a constatação",IF(AND(H64="Não conformidade",J64="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5253,7 +5256,7 @@
         <v/>
       </c>
       <c r="K65" s="18" t="str">
-        <f aca="false">IF(AND(C65="",D65="",COUNTA(E65:H65)=0),"",IF(D65="","Falta o requisito",IF(C65="","Falta a pergunta",IF(N(I65)=0,"Falta a evidência",IF(H65="","Falta a constatação",IF(AND(H65="Não conformidade",J65&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C65="",D65="",COUNTA(E65:H65)=0),"",IF(D65="","Falta o requisito",IF(C65="","Falta a pergunta",IF(N(I65)=0,"Falta a evidência",IF(H65="","Falta a constatação",IF(AND(H65="Não conformidade",J65="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5276,7 +5279,7 @@
         <v/>
       </c>
       <c r="K66" s="18" t="str">
-        <f aca="false">IF(AND(C66="",D66="",COUNTA(E66:H66)=0),"",IF(D66="","Falta o requisito",IF(C66="","Falta a pergunta",IF(N(I66)=0,"Falta a evidência",IF(H66="","Falta a constatação",IF(AND(H66="Não conformidade",J66&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK"))))))</f>
+        <f aca="false">IF(AND(C66="",D66="",COUNTA(E66:H66)=0),"",IF(D66="","Falta o requisito",IF(C66="","Falta a pergunta",IF(N(I66)=0,"Falta a evidência",IF(H66="","Falta a constatação",IF(AND(H66="Não conformidade",J66="Fraca"),"Não conformidade sem evidência objetiva","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -5335,7 +5338,7 @@
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="22" t="str">
-        <f aca="false">IF(COUNTA(C7:C66)=0,"Registre as perguntas e as evidências",IF(COUNTIF(K7:K66,"Não conformidade sem corroboração")&gt;0,"Há não conformidade sem corroboração: busque outra fonte",IF(SUMPRODUCT((K7:K66&lt;&gt;"")*(K7:K66&lt;&gt;"OK"))&gt;0,"Há pergunta a completar: veja a coluna Conferência","OK")))</f>
+        <f aca="false">IF(COUNTA(C7:C66)=0,"Registre as perguntas e as evidências",IF(COUNTIF(K7:K66,"Não conformidade sem evidência objetiva")&gt;0,"Há não conformidade sem evidência objetiva: busque registro ou observação",IF(SUMPRODUCT((K7:K66&lt;&gt;"")*(K7:K66&lt;&gt;"OK"))&gt;0,"Há pergunta a completar: veja a coluna Conferência","OK")))</f>
         <v>Registre as perguntas e as evidências</v>
       </c>
       <c r="F71" s="22"/>
@@ -5384,7 +5387,7 @@
       <formula>K7="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>K7="Não conformidade sem corroboração"</formula>
+      <formula>K7="Não conformidade sem evidência objetiva"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>LEN(K7)&gt;0</formula>
@@ -6100,7 +6103,7 @@
         <v>180</v>
       </c>
       <c r="C11" s="15" t="n">
-        <f aca="false">COUNTIF(Amostras!N12:N41,"Desvio isolado: ampliar a amostra")</f>
+        <f aca="false">COUNTIF(Amostras!N12:N41,"Desvio pontual: não conformidade, ampliar a amostra")</f>
         <v>0</v>
       </c>
       <c r="D11" s="27" t="s">
@@ -6207,7 +6210,7 @@
         <v>193</v>
       </c>
       <c r="C19" s="15" t="n">
-        <f aca="false">COUNTIF(Evidências!K7:K66,"Não conformidade sem corroboração")</f>
+        <f aca="false">COUNTIF(Evidências!K7:K66,"Não conformidade sem evidência objetiva")</f>
         <v>0</v>
       </c>
       <c r="D19" s="27" t="s">
@@ -6309,7 +6312,7 @@
         <v>113</v>
       </c>
       <c r="C28" s="22" t="str">
-        <f aca="false">IF(C7+C15=0,"Preencha as abas Amostras e Evidências",IF(C19&gt;0,"Há não conformidade sem corroboração",IF(C11&gt;0,"Há desvio isolado: amplie a amostra",IF(C13&gt;0,"Há amostra incompleta",IF(C25&gt;0,"Há linha a completar: veja as conferências",IF(C24&gt;0,"Há auditor em formação: planeje o acompanhamento","OK"))))))</f>
+        <f aca="false">IF(C7+C15=0,"Preencha as abas Amostras e Evidências",IF(C19&gt;0,"Há não conformidade sem evidência objetiva",IF(C11&gt;0,"Há desvio pontual: amplie a amostra",IF(C13&gt;0,"Há amostra incompleta",IF(C25&gt;0,"Há linha a completar: veja as conferências",IF(C24&gt;0,"Há auditor em formação: planeje o acompanhamento","OK"))))))</f>
         <v>Preencha as abas Amostras e Evidências</v>
       </c>
       <c r="D28" s="22"/>
@@ -6330,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
         <v>33</v>
       </c>
@@ -6685,7 +6688,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:O57"/>
+  <dimension ref="B1:O58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -6971,7 +6974,7 @@
         <v>245</v>
       </c>
       <c r="N14" s="17" t="str">
-        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Desvio repetido: não conformidade</v>
       </c>
       <c r="O14" s="18" t="str">
@@ -7019,8 +7022,8 @@
         <v>248</v>
       </c>
       <c r="N15" s="17" t="str">
-        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
-        <v>Desvio isolado: ampliar a amostra</v>
+        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <v>Desvio pontual: não conformidade, ampliar a amostra</v>
       </c>
       <c r="O15" s="18" t="str">
         <f aca="false">IF(C15="","",IF(N(F15)=0,"Falta a população",IF(G15="","Falta o risco",IF(OR(H15="",H15&lt;1,H15&gt;J15),"Início deve ir de 1 a "&amp;J15,IF(K15="","Falta quantos foram verificados",IF(K15&gt;F15,"Verificados acima da população",IF(L15="","Falta quantos desvios",IF(L15&gt;K15,"Mais desvios que verificados","OK"))))))))</f>
@@ -7065,7 +7068,7 @@
       </c>
       <c r="M16" s="34"/>
       <c r="N16" s="17" t="str">
-        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Conforme na amostra</v>
       </c>
       <c r="O16" s="18" t="str">
@@ -7111,7 +7114,7 @@
       </c>
       <c r="M17" s="34"/>
       <c r="N17" s="17" t="str">
-        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Conforme na amostra</v>
       </c>
       <c r="O17" s="18" t="str">
@@ -7159,7 +7162,7 @@
         <v>255</v>
       </c>
       <c r="N18" s="17" t="str">
-        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Amostra incompleta</v>
       </c>
       <c r="O18" s="18" t="str">
@@ -7250,7 +7253,7 @@
         <v>Forte</v>
       </c>
       <c r="N22" s="18" t="str">
-        <f aca="false">IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(COUNTA(E22,F22,H22)=0,"Falta a evidência",IF(K22="","Falta a constatação",IF(AND(K22="Não conformidade",M22&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(COUNTA(E22,F22,H22)=0,"Falta a evidência",IF(K22="","Falta a constatação",IF(AND(K22="Não conformidade",M22="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O22" s="18"/>
@@ -7284,7 +7287,7 @@
         <v>Forte</v>
       </c>
       <c r="N23" s="18" t="str">
-        <f aca="false">IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(COUNTA(E23,F23,H23)=0,"Falta a evidência",IF(K23="","Falta a constatação",IF(AND(K23="Não conformidade",M23&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(COUNTA(E23,F23,H23)=0,"Falta a evidência",IF(K23="","Falta a constatação",IF(AND(K23="Não conformidade",M23="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O23" s="18"/>
@@ -7297,30 +7300,26 @@
         <v>265</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>266</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I24" s="34"/>
       <c r="J24" s="34"/>
       <c r="K24" s="38" t="s">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="L24" s="38"/>
       <c r="M24" s="39" t="str">
         <f aca="false">IF(COUNTA(E24,F24,H24)=0,"",IF(COUNTA(E24,F24,H24)&gt;=2,"Forte",IF(OR(F24&lt;&gt;"",H24&lt;&gt;""),"Média","Fraca")))</f>
-        <v>Forte</v>
+        <v>Média</v>
       </c>
       <c r="N24" s="18" t="str">
-        <f aca="false">IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(COUNTA(E24,F24,H24)=0,"Falta a evidência",IF(K24="","Falta a constatação",IF(AND(K24="Não conformidade",M24&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(COUNTA(E24,F24,H24)=0,"Falta a evidência",IF(K24="","Falta a constatação",IF(AND(K24="Não conformidade",M24="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O24" s="18"/>
@@ -7330,18 +7329,20 @@
         <v>4</v>
       </c>
       <c r="C25" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="D25" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="F25" s="34"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I25" s="34"/>
       <c r="J25" s="34"/>
@@ -7354,7 +7355,7 @@
         <v>Forte</v>
       </c>
       <c r="N25" s="18" t="str">
-        <f aca="false">IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(COUNTA(E25,F25,H25)=0,"Falta a evidência",IF(K25="","Falta a constatação",IF(AND(K25="Não conformidade",M25&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(COUNTA(E25,F25,H25)=0,"Falta a evidência",IF(K25="","Falta a constatação",IF(AND(K25="Não conformidade",M25="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O25" s="18"/>
@@ -7364,30 +7365,32 @@
         <v>5</v>
       </c>
       <c r="C26" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="E26" s="34" t="s">
         <v>271</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>273</v>
       </c>
       <c r="F26" s="34"/>
       <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
+      <c r="H26" s="34" t="s">
+        <v>272</v>
+      </c>
       <c r="I26" s="34"/>
       <c r="J26" s="34"/>
       <c r="K26" s="38" t="s">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="L26" s="38"/>
       <c r="M26" s="39" t="str">
         <f aca="false">IF(COUNTA(E26,F26,H26)=0,"",IF(COUNTA(E26,F26,H26)&gt;=2,"Forte",IF(OR(F26&lt;&gt;"",H26&lt;&gt;""),"Média","Fraca")))</f>
-        <v>Fraca</v>
+        <v>Forte</v>
       </c>
       <c r="N26" s="18" t="str">
-        <f aca="false">IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(COUNTA(E26,F26,H26)=0,"Falta a evidência",IF(K26="","Falta a constatação",IF(AND(K26="Não conformidade",M26&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
-        <v>Não conformidade sem corroboração</v>
+        <f aca="false">IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(COUNTA(E26,F26,H26)=0,"Falta a evidência",IF(K26="","Falta a constatação",IF(AND(K26="Não conformidade",M26="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
+        <v>OK</v>
       </c>
       <c r="O26" s="18"/>
     </row>
@@ -7396,32 +7399,30 @@
         <v>6</v>
       </c>
       <c r="C27" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="E27" s="34" t="s">
         <v>275</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>269</v>
       </c>
       <c r="F27" s="34"/>
       <c r="G27" s="34"/>
-      <c r="H27" s="34" t="s">
-        <v>276</v>
-      </c>
+      <c r="H27" s="34"/>
       <c r="I27" s="34"/>
       <c r="J27" s="34"/>
       <c r="K27" s="38" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="L27" s="38"/>
       <c r="M27" s="39" t="str">
         <f aca="false">IF(COUNTA(E27,F27,H27)=0,"",IF(COUNTA(E27,F27,H27)&gt;=2,"Forte",IF(OR(F27&lt;&gt;"",H27&lt;&gt;""),"Média","Fraca")))</f>
-        <v>Forte</v>
+        <v>Fraca</v>
       </c>
       <c r="N27" s="18" t="str">
-        <f aca="false">IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(COUNTA(E27,F27,H27)=0,"Falta a evidência",IF(K27="","Falta a constatação",IF(AND(K27="Não conformidade",M27&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
-        <v>OK</v>
+        <f aca="false">IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(COUNTA(E27,F27,H27)=0,"Falta a evidência",IF(K27="","Falta a constatação",IF(AND(K27="Não conformidade",M27="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
+        <v>Não conformidade sem evidência objetiva</v>
       </c>
       <c r="O27" s="18"/>
     </row>
@@ -7430,23 +7431,23 @@
         <v>7</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34" t="s">
-        <v>280</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="F28" s="34"/>
       <c r="G28" s="34"/>
       <c r="H28" s="34" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="34"/>
       <c r="K28" s="38" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="L28" s="38"/>
       <c r="M28" s="39" t="str">
@@ -7454,7 +7455,7 @@
         <v>Forte</v>
       </c>
       <c r="N28" s="18" t="str">
-        <f aca="false">IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(COUNTA(E28,F28,H28)=0,"Falta a evidência",IF(K28="","Falta a constatação",IF(AND(K28="Não conformidade",M28&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(COUNTA(E28,F28,H28)=0,"Falta a evidência",IF(K28="","Falta a constatação",IF(AND(K28="Não conformidade",M28="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O28" s="18"/>
@@ -7464,23 +7465,23 @@
         <v>8</v>
       </c>
       <c r="C29" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="G29" s="34"/>
+      <c r="H29" s="34" t="s">
         <v>283</v>
       </c>
-      <c r="E29" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
       <c r="I29" s="34"/>
       <c r="J29" s="34"/>
       <c r="K29" s="38" t="s">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="L29" s="38"/>
       <c r="M29" s="39" t="str">
@@ -7488,7 +7489,7 @@
         <v>Forte</v>
       </c>
       <c r="N29" s="18" t="str">
-        <f aca="false">IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(COUNTA(E29,F29,H29)=0,"Falta a evidência",IF(K29="","Falta a constatação",IF(AND(K29="Não conformidade",M29&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(COUNTA(E29,F29,H29)=0,"Falta a evidência",IF(K29="","Falta a constatação",IF(AND(K29="Não conformidade",M29="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O29" s="18"/>
@@ -7498,13 +7499,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="34" t="s">
         <v>286</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>284</v>
       </c>
       <c r="F30" s="34" t="s">
         <v>287</v>
@@ -7513,96 +7514,110 @@
       <c r="H30" s="34"/>
       <c r="I30" s="34"/>
       <c r="J30" s="34"/>
-      <c r="K30" s="38"/>
+      <c r="K30" s="38" t="s">
+        <v>130</v>
+      </c>
       <c r="L30" s="38"/>
       <c r="M30" s="39" t="str">
         <f aca="false">IF(COUNTA(E30,F30,H30)=0,"",IF(COUNTA(E30,F30,H30)&gt;=2,"Forte",IF(OR(F30&lt;&gt;"",H30&lt;&gt;""),"Média","Fraca")))</f>
         <v>Forte</v>
       </c>
       <c r="N30" s="18" t="str">
-        <f aca="false">IF(D30="","Falta o requisito",IF(C30="","Falta a pergunta",IF(COUNTA(E30,F30,H30)=0,"Falta a evidência",IF(K30="","Falta a constatação",IF(AND(K30="Não conformidade",M30&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D30="","Falta o requisito",IF(C30="","Falta a pergunta",IF(COUNTA(E30,F30,H30)=0,"Falta a evidência",IF(K30="","Falta a constatação",IF(AND(K30="Não conformidade",M30="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
+        <v>OK</v>
+      </c>
+      <c r="O30" s="18"/>
+    </row>
+    <row r="31" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="39" t="str">
+        <f aca="false">IF(COUNTA(E31,F31,H31)=0,"",IF(COUNTA(E31,F31,H31)&gt;=2,"Forte",IF(OR(F31&lt;&gt;"",H31&lt;&gt;""),"Média","Fraca")))</f>
+        <v>Forte</v>
+      </c>
+      <c r="N31" s="18" t="str">
+        <f aca="false">IF(D31="","Falta o requisito",IF(C31="","Falta a pergunta",IF(COUNTA(E31,F31,H31)=0,"Falta a evidência",IF(K31="","Falta a constatação",IF(AND(K31="Não conformidade",M31="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>Falta a constatação</v>
       </c>
-      <c r="O30" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="40" t="s">
+      <c r="O31" s="18"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-    </row>
-    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
+    </row>
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D34" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F34" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G34" s="15" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="38" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G34" s="38" t="s">
+      <c r="G35" s="38" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F35" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D36" s="24" t="s">
         <v>145</v>
@@ -7619,48 +7634,48 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>146</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="33"/>
+        <v>2</v>
+      </c>
+      <c r="G37" s="33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>146</v>
       </c>
       <c r="F38" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="33" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G38" s="33"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D39" s="24" t="s">
         <v>116</v>
@@ -7669,7 +7684,7 @@
         <v>146</v>
       </c>
       <c r="F39" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="33" t="n">
         <v>2</v>
@@ -7677,19 +7692,19 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>153</v>
+        <v>116</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="F40" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" s="33" t="n">
         <v>2</v>
@@ -7697,248 +7712,247 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D41" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E41" s="24" t="s">
-        <v>146</v>
+      <c r="E41" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="F41" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="33" t="n">
         <v>2</v>
-      </c>
-      <c r="G41" s="33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>153</v>
+        <v>89</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="F42" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="33" t="n">
         <v>1</v>
-      </c>
-      <c r="G42" s="33" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D43" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="E43" s="24" t="s">
-        <v>146</v>
+      <c r="E43" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="F43" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="33" t="n">
         <v>2</v>
-      </c>
-      <c r="G43" s="33" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="F44" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="33"/>
+      <c r="G44" s="33" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D45" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="E45" s="24" t="s">
-        <v>146</v>
+      <c r="E45" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" s="33" t="n">
         <v>2</v>
       </c>
+      <c r="G45" s="33"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="E46" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="33"/>
+      <c r="F46" s="33" t="n">
+        <v>3</v>
+      </c>
       <c r="G46" s="33" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="16" t="n">
-        <f aca="false">IF(F$33="","",COUNT(F35:F46))</f>
-        <v>11</v>
-      </c>
-      <c r="G47" s="16" t="n">
-        <f aca="false">IF(G$33="","",COUNT(G35:G46))</f>
-        <v>10</v>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
       <c r="F48" s="16" t="n">
-        <f aca="false">IF(F$33="","",SUM(F35:F46))</f>
-        <v>23</v>
+        <f aca="false">IF(F$34="","",COUNT(F36:F47))</f>
+        <v>11</v>
       </c>
       <c r="G48" s="16" t="n">
-        <f aca="false">IF(G$33="","",SUM(G35:G46))</f>
-        <v>18</v>
+        <f aca="false">IF(G$34="","",COUNT(G36:G47))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
-      <c r="F49" s="25" t="n">
-        <f aca="false">IF(OR(F$33="",N(F47)=0),"",F48/(3*F47))</f>
-        <v>0.696969696969697</v>
-      </c>
-      <c r="G49" s="25" t="n">
-        <f aca="false">IF(OR(G$33="",N(G47)=0),"",G48/(3*G47))</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F49" s="16" t="n">
+        <f aca="false">IF(F$34="","",SUM(F36:F47))</f>
+        <v>23</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <f aca="false">IF(G$34="","",SUM(G36:G47))</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
-      <c r="F50" s="39" t="str">
-        <f aca="false">IF(F$33="","",IF(F47=0,"",IF(F47&lt;8,"Observação insuficiente",IF(SUMPRODUCT(($E$35:$E$46="Sim")*(F35:F46&lt;&gt;"")*(F35:F46&lt;=1))&gt;0,"Em formação",IF(F49&gt;=0.8-0.000000001,"Apto a liderar",IF(F49&gt;=0.6-0.000000001,"Apto a auditar em equipe","Em formação"))))))</f>
-        <v>Em formação</v>
-      </c>
-      <c r="G50" s="39" t="str">
-        <f aca="false">IF(G$33="","",IF(G47=0,"",IF(G47&lt;8,"Observação insuficiente",IF(SUMPRODUCT(($E$35:$E$46="Sim")*(G35:G46&lt;&gt;"")*(G35:G46&lt;=1))&gt;0,"Em formação",IF(G49&gt;=0.8-0.000000001,"Apto a liderar",IF(G49&gt;=0.6-0.000000001,"Apto a auditar em equipe","Em formação"))))))</f>
-        <v>Apto a auditar em equipe</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F50" s="25" t="n">
+        <f aca="false">IF(OR(F$34="",N(F48)=0),"",F49/(3*F48))</f>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <f aca="false">IF(OR(G$34="",N(G48)=0),"",G49/(3*G48))</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="20" t="s">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
-      <c r="F51" s="18" t="str">
-        <f aca="false">IF(F$33="",IF(COUNT(F35:F46)&gt;0,"Falta o nome",""),IF(F47=0,"Faltam as notas",IF(F47&lt;8,"Observar mais critérios","OK")))</f>
+      <c r="F51" s="39" t="str">
+        <f aca="false">IF(F$34="","",IF(F48=0,"",IF(F48&lt;8,"Observação insuficiente",IF(SUMPRODUCT(($E$36:$E$47="Sim")*(F36:F47&lt;&gt;"")*(F36:F47&lt;=1))&gt;0,"Em formação",IF(F50&gt;=0.8-0.000000001,"Apto a liderar",IF(F50&gt;=0.6-0.000000001,"Apto a auditar em equipe","Em formação"))))))</f>
+        <v>Em formação</v>
+      </c>
+      <c r="G51" s="39" t="str">
+        <f aca="false">IF(G$34="","",IF(G48=0,"",IF(G48&lt;8,"Observação insuficiente",IF(SUMPRODUCT(($E$36:$E$47="Sim")*(G36:G47&lt;&gt;"")*(G36:G47&lt;=1))&gt;0,"Em formação",IF(G50&gt;=0.8-0.000000001,"Apto a liderar",IF(G50&gt;=0.6-0.000000001,"Apto a auditar em equipe","Em formação"))))))</f>
+        <v>Apto a auditar em equipe</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="18" t="str">
+        <f aca="false">IF(F$34="",IF(COUNT(F36:F47)&gt;0,"Falta o nome",""),IF(F48=0,"Faltam as notas",IF(F48&lt;8,"Observar mais critérios","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="G51" s="18" t="str">
-        <f aca="false">IF(G$33="",IF(COUNT(G35:G46)&gt;0,"Falta o nome",""),IF(G47=0,"Faltam as notas",IF(G47&lt;8,"Observar mais critérios","OK")))</f>
+      <c r="G52" s="18" t="str">
+        <f aca="false">IF(G$34="",IF(COUNT(G36:G47)&gt;0,"Falta o nome",""),IF(G48=0,"Faltam as notas",IF(G48&lt;8,"Observar mais critérios","OK")))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="19" t="s">
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="19"/>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-    </row>
-    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="21" t="str">
-        <f aca="false">SUM(K14:K18)&amp;" registros verificados em "&amp;COUNTA(C14:C18)&amp;" amostras, "&amp;SUM(L14:L18)&amp;" desvios. "&amp;COUNTIF(N14:N18,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio isolado: ampliar a amostra")&amp;" desvio isolado: ampliar a amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N14:N18,"Amostra incompleta")&amp;" amostra incompleta"</f>
-        <v>51 registros verificados em 5 amostras, 4 desvios. 2 conforme na amostra, 1 desvio isolado: ampliar a amostra, 1 desvio repetido: não conformidade, 1 amostra incompleta</v>
-      </c>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
-      <c r="O54" s="21"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
       <c r="E55" s="21" t="str">
-        <f aca="false">COUNTIF(K22:L30,"Conforme")&amp;" conforme"&amp;", "&amp;COUNTIF(K22:L30,"Não conformidade")&amp;" não conformidade"&amp;", "&amp;COUNTIF(K22:L30,"Oportunidade de melhoria")&amp;" oportunidade de melhoria"&amp;". Força: "&amp;COUNTIF(M22:M30,"Forte")&amp;" forte"&amp;", "&amp;COUNTIF(M22:M30,"Média")&amp;" média"&amp;", "&amp;COUNTIF(M22:M30,"Fraca")&amp;" fraca"</f>
-        <v>3 conforme, 4 não conformidade, 1 oportunidade de melhoria. Força: 8 forte, 0 média, 1 fraca</v>
+        <f aca="false">SUM(K14:K18)&amp;" registros verificados em "&amp;COUNTA(C14:C18)&amp;" amostras, "&amp;SUM(L14:L18)&amp;" desvios. "&amp;COUNTIF(N14:N18,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio pontual: não conformidade, ampliar a amostra")&amp;" desvio pontual: não conformidade, ampliar a amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N14:N18,"Amostra incompleta")&amp;" amostra incompleta"</f>
+        <v>51 registros verificados em 5 amostras, 4 desvios. 2 conforme na amostra, 1 desvio pontual: não conformidade, ampliar a amostra, 1 desvio repetido: não conformidade, 1 amostra incompleta</v>
       </c>
       <c r="F55" s="21"/>
       <c r="G55" s="21"/>
@@ -7953,13 +7967,13 @@
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="21" t="str">
-        <f aca="false">COUNTIF(F50:G50,"Apto a liderar")&amp;" apto a liderar"&amp;", "&amp;COUNTIF(F50:G50,"Apto a auditar em equipe")&amp;" apto a auditar em equipe"&amp;", "&amp;COUNTIF(F50:G50,"Em formação")&amp;" em formação"&amp;", "&amp;COUNTIF(F50:G50,"Observação insuficiente")&amp;" observação insuficiente"</f>
-        <v>0 apto a liderar, 1 apto a auditar em equipe, 1 em formação, 0 observação insuficiente</v>
+        <f aca="false">COUNTIF(K22:L31,"Conforme")&amp;" conforme"&amp;", "&amp;COUNTIF(K22:L31,"Não conformidade")&amp;" não conformidade"&amp;", "&amp;COUNTIF(K22:L31,"Oportunidade de melhoria")&amp;" oportunidade de melhoria"&amp;". Força: "&amp;COUNTIF(M22:M31,"Forte")&amp;" forte"&amp;", "&amp;COUNTIF(M22:M31,"Média")&amp;" média"&amp;", "&amp;COUNTIF(M22:M31,"Fraca")&amp;" fraca"</f>
+        <v>3 conforme, 5 não conformidade, 1 oportunidade de melhoria. Força: 8 forte, 1 média, 1 fraca</v>
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="21"/>
@@ -7974,13 +7988,13 @@
     </row>
     <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="20" t="s">
-        <v>203</v>
+        <v>61</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="21" t="n">
-        <f aca="false">SUMPRODUCT((O14:O18&lt;&gt;"OK")*1)+SUMPRODUCT((N22:N30&lt;&gt;"OK")*1)</f>
-        <v>2</v>
+      <c r="E57" s="21" t="str">
+        <f aca="false">COUNTIF(F51:G51,"Apto a liderar")&amp;" apto a liderar"&amp;", "&amp;COUNTIF(F51:G51,"Apto a auditar em equipe")&amp;" apto a auditar em equipe"&amp;", "&amp;COUNTIF(F51:G51,"Em formação")&amp;" em formação"&amp;", "&amp;COUNTIF(F51:G51,"Observação insuficiente")&amp;" observação insuficiente"</f>
+        <v>0 apto a liderar, 1 apto a auditar em equipe, 1 em formação, 0 observação insuficiente</v>
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="21"/>
@@ -7993,8 +8007,29 @@
       <c r="N57" s="21"/>
       <c r="O57" s="21"/>
     </row>
+    <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="21" t="n">
+        <f aca="false">SUMPRODUCT((O14:O18&lt;&gt;"OK")*1)+SUMPRODUCT((N22:N31&lt;&gt;"OK")*1)</f>
+        <v>2</v>
+      </c>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="77">
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B4:C4"/>
@@ -8052,29 +8087,33 @@
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="N30:O30"/>
-    <mergeCell ref="B32:O32"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B53:O53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B54:O54"/>
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="E55:O55"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="E56:O56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="E57:O57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:O58"/>
   </mergeCells>
   <conditionalFormatting sqref="N14:N18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>N14="Conforme na amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>N14="Desvio isolado: ampliar a amostra"</formula>
+      <formula>N14="Desvio pontual: não conformidade, ampliar a amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>N14="Amostra incompleta"</formula>
@@ -8091,7 +8130,7 @@
       <formula>AND(LEN(O14)&gt;0,NOT(OR(O14="OK")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M22:M30">
+  <conditionalFormatting sqref="M22:M31">
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>M22="Forte"</formula>
     </cfRule>
@@ -8102,7 +8141,7 @@
       <formula>M22="Fraca"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K22:L30">
+  <conditionalFormatting sqref="K22:L31">
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K22="Conforme"</formula>
     </cfRule>
@@ -8113,42 +8152,42 @@
       <formula>$K22="Oportunidade de melhoria"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N22:O30">
+  <conditionalFormatting sqref="N22:O31">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$N22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>$N22="Não conformidade sem corroboração"</formula>
+      <formula>$N22="Não conformidade sem evidência objetiva"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>LEN($N22)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F50:G50">
+  <conditionalFormatting sqref="F51:G51">
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>F50="Apto a liderar"</formula>
+      <formula>F51="Apto a liderar"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>F50="Apto a auditar em equipe"</formula>
+      <formula>F51="Apto a auditar em equipe"</formula>
     </cfRule>
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>F50="Em formação"</formula>
+      <formula>F51="Em formação"</formula>
     </cfRule>
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>F50="Observação insuficiente"</formula>
+      <formula>F51="Observação insuficiente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F51:G51">
+  <conditionalFormatting sqref="F52:G52">
     <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>OR(F51="OK")</formula>
+      <formula>OR(F52="OK")</formula>
     </cfRule>
     <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>AND(LEN(F51)&gt;0,NOT(OR(F51="OK")))</formula>
+      <formula>AND(LEN(F52)&gt;0,NOT(OR(F52="OK")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35:G46">
+  <conditionalFormatting sqref="F36:G47">
     <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>AND($E35="Sim",F35&lt;&gt;"",F35&lt;=1)</formula>
+      <formula>AND($E36="Sim",F36&lt;&gt;"",F36&lt;=1)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -8160,7 +8199,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="19" man="true" max="16383" min="0"/>
-    <brk id="31" man="true" max="16383" min="0"/>
+    <brk id="32" man="true" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -8232,7 +8271,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E4" s="29"/>
       <c r="F4" s="29"/>
@@ -8252,7 +8291,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E5" s="29"/>
       <c r="F5" s="29"/>
@@ -8272,7 +8311,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
@@ -8292,7 +8331,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E7" s="29"/>
       <c r="F7" s="29"/>
@@ -8312,7 +8351,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
@@ -8332,7 +8371,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="29" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
@@ -8422,13 +8461,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>242</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F14" s="35" t="n">
         <v>1150</v>
@@ -8455,7 +8494,7 @@
       </c>
       <c r="M14" s="34"/>
       <c r="N14" s="17" t="str">
-        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I14="",K14="",L14=""),"",IF(K14&lt;I14,"Amostra incompleta",IF(L14=0,"Conforme na amostra",IF(L14=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Conforme na amostra</v>
       </c>
       <c r="O14" s="18" t="str">
@@ -8468,13 +8507,13 @@
         <v>2</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>9</v>
@@ -8500,10 +8539,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N15" s="17" t="str">
-        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I15="",K15="",L15=""),"",IF(K15&lt;I15,"Amostra incompleta",IF(L15=0,"Conforme na amostra",IF(L15=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Desvio repetido: não conformidade</v>
       </c>
       <c r="O15" s="18" t="str">
@@ -8516,13 +8555,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>14</v>
@@ -8548,11 +8587,11 @@
         <v>1</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N16" s="17" t="str">
-        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
-        <v>Desvio isolado: ampliar a amostra</v>
+        <f aca="false">IF(OR(I16="",K16="",L16=""),"",IF(K16&lt;I16,"Amostra incompleta",IF(L16=0,"Conforme na amostra",IF(L16=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <v>Desvio pontual: não conformidade, ampliar a amostra</v>
       </c>
       <c r="O16" s="18" t="str">
         <f aca="false">IF(C16="","",IF(N(F16)=0,"Falta a população",IF(G16="","Falta o risco",IF(OR(H16="",H16&lt;1,H16&gt;J16),"Início deve ir de 1 a "&amp;J16,IF(K16="","Falta quantos foram verificados",IF(K16&gt;F16,"Verificados acima da população",IF(L16="","Falta quantos desvios",IF(L16&gt;K16,"Mais desvios que verificados","OK"))))))))</f>
@@ -8564,13 +8603,13 @@
         <v>4</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>262</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>25</v>
@@ -8597,7 +8636,7 @@
       </c>
       <c r="M17" s="34"/>
       <c r="N17" s="17" t="str">
-        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I17="",K17="",L17=""),"",IF(K17&lt;I17,"Amostra incompleta",IF(L17=0,"Conforme na amostra",IF(L17=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Conforme na amostra</v>
       </c>
       <c r="O17" s="18" t="str">
@@ -8610,13 +8649,13 @@
         <v>5</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>251</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F18" s="35" t="n">
         <v>12</v>
@@ -8643,7 +8682,7 @@
       </c>
       <c r="M18" s="34"/>
       <c r="N18" s="17" t="str">
-        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio isolado: ampliar a amostra","Desvio repetido: não conformidade"))))</f>
+        <f aca="false">IF(OR(I18="",K18="",L18=""),"",IF(K18&lt;I18,"Amostra incompleta",IF(L18=0,"Conforme na amostra",IF(L18=1,"Desvio pontual: não conformidade, ampliar a amostra","Desvio repetido: não conformidade"))))</f>
         <v>Conforme na amostra</v>
       </c>
       <c r="O18" s="18" t="str">
@@ -8708,18 +8747,18 @@
         <v>1</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I22" s="34"/>
       <c r="J22" s="34"/>
@@ -8732,7 +8771,7 @@
         <v>Forte</v>
       </c>
       <c r="N22" s="18" t="str">
-        <f aca="false">IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(COUNTA(E22,F22,H22)=0,"Falta a evidência",IF(K22="","Falta a constatação",IF(AND(K22="Não conformidade",M22&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D22="","Falta o requisito",IF(C22="","Falta a pergunta",IF(COUNTA(E22,F22,H22)=0,"Falta a evidência",IF(K22="","Falta a constatação",IF(AND(K22="Não conformidade",M22="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O22" s="18"/>
@@ -8742,20 +8781,20 @@
         <v>2</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>242</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G23" s="34"/>
       <c r="H23" s="34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I23" s="34"/>
       <c r="J23" s="34"/>
@@ -8768,7 +8807,7 @@
         <v>Forte</v>
       </c>
       <c r="N23" s="18" t="str">
-        <f aca="false">IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(COUNTA(E23,F23,H23)=0,"Falta a evidência",IF(K23="","Falta a constatação",IF(AND(K23="Não conformidade",M23&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D23="","Falta o requisito",IF(C23="","Falta a pergunta",IF(COUNTA(E23,F23,H23)=0,"Falta a evidência",IF(K23="","Falta a constatação",IF(AND(K23="Não conformidade",M23="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O23" s="18"/>
@@ -8778,23 +8817,23 @@
         <v>3</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I24" s="34"/>
       <c r="J24" s="34"/>
       <c r="K24" s="38" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="L24" s="38"/>
       <c r="M24" s="39" t="str">
@@ -8802,7 +8841,7 @@
         <v>Forte</v>
       </c>
       <c r="N24" s="18" t="str">
-        <f aca="false">IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(COUNTA(E24,F24,H24)=0,"Falta a evidência",IF(K24="","Falta a constatação",IF(AND(K24="Não conformidade",M24&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D24="","Falta o requisito",IF(C24="","Falta a pergunta",IF(COUNTA(E24,F24,H24)=0,"Falta a evidência",IF(K24="","Falta a constatação",IF(AND(K24="Não conformidade",M24="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O24" s="18"/>
@@ -8812,20 +8851,20 @@
         <v>4</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G25" s="34"/>
       <c r="H25" s="34" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I25" s="34"/>
       <c r="J25" s="34"/>
@@ -8838,7 +8877,7 @@
         <v>Forte</v>
       </c>
       <c r="N25" s="18" t="str">
-        <f aca="false">IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(COUNTA(E25,F25,H25)=0,"Falta a evidência",IF(K25="","Falta a constatação",IF(AND(K25="Não conformidade",M25&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D25="","Falta o requisito",IF(C25="","Falta a pergunta",IF(COUNTA(E25,F25,H25)=0,"Falta a evidência",IF(K25="","Falta a constatação",IF(AND(K25="Não conformidade",M25="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O25" s="18"/>
@@ -8848,18 +8887,18 @@
         <v>5</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>262</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G26" s="34"/>
       <c r="H26" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I26" s="34"/>
       <c r="J26" s="34"/>
@@ -8872,7 +8911,7 @@
         <v>Forte</v>
       </c>
       <c r="N26" s="18" t="str">
-        <f aca="false">IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(COUNTA(E26,F26,H26)=0,"Falta a evidência",IF(K26="","Falta a constatação",IF(AND(K26="Não conformidade",M26&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D26="","Falta o requisito",IF(C26="","Falta a pergunta",IF(COUNTA(E26,F26,H26)=0,"Falta a evidência",IF(K26="","Falta a constatação",IF(AND(K26="Não conformidade",M26="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O26" s="18"/>
@@ -8882,13 +8921,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F27" s="34"/>
       <c r="G27" s="34"/>
@@ -8904,8 +8943,8 @@
         <v>Fraca</v>
       </c>
       <c r="N27" s="18" t="str">
-        <f aca="false">IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(COUNTA(E27,F27,H27)=0,"Falta a evidência",IF(K27="","Falta a constatação",IF(AND(K27="Não conformidade",M27&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
-        <v>Não conformidade sem corroboração</v>
+        <f aca="false">IF(D27="","Falta o requisito",IF(C27="","Falta a pergunta",IF(COUNTA(E27,F27,H27)=0,"Falta a evidência",IF(K27="","Falta a constatação",IF(AND(K27="Não conformidade",M27="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
+        <v>Não conformidade sem evidência objetiva</v>
       </c>
       <c r="O27" s="18"/>
     </row>
@@ -8914,18 +8953,18 @@
         <v>7</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="34"/>
       <c r="H28" s="34" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="34"/>
@@ -8938,7 +8977,7 @@
         <v>Forte</v>
       </c>
       <c r="N28" s="18" t="str">
-        <f aca="false">IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(COUNTA(E28,F28,H28)=0,"Falta a evidência",IF(K28="","Falta a constatação",IF(AND(K28="Não conformidade",M28&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D28="","Falta o requisito",IF(C28="","Falta a pergunta",IF(COUNTA(E28,F28,H28)=0,"Falta a evidência",IF(K28="","Falta a constatação",IF(AND(K28="Não conformidade",M28="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O28" s="18"/>
@@ -8948,20 +8987,20 @@
         <v>8</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G29" s="34"/>
       <c r="H29" s="34" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I29" s="34"/>
       <c r="J29" s="34"/>
@@ -8974,7 +9013,7 @@
         <v>Forte</v>
       </c>
       <c r="N29" s="18" t="str">
-        <f aca="false">IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(COUNTA(E29,F29,H29)=0,"Falta a evidência",IF(K29="","Falta a constatação",IF(AND(K29="Não conformidade",M29&lt;&gt;"Forte"),"Não conformidade sem corroboração","OK")))))</f>
+        <f aca="false">IF(D29="","Falta o requisito",IF(C29="","Falta a pergunta",IF(COUNTA(E29,F29,H29)=0,"Falta a evidência",IF(K29="","Falta a constatação",IF(AND(K29="Não conformidade",M29="Fraca"),"Não conformidade sem evidência objetiva","OK")))))</f>
         <v>OK</v>
       </c>
       <c r="O29" s="18"/>
@@ -9011,18 +9050,18 @@
         <v>139</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="41" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
@@ -9034,7 +9073,7 @@
         <v>135</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9428,8 +9467,8 @@
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="21" t="str">
-        <f aca="false">SUM(K14:K18)&amp;" registros verificados em "&amp;COUNTA(C14:C18)&amp;" amostras, "&amp;SUM(L14:L18)&amp;" desvios. "&amp;COUNTIF(N14:N18,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio isolado: ampliar a amostra")&amp;" desvio isolado: ampliar a amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N14:N18,"Amostra incompleta")&amp;" amostra incompleta"</f>
-        <v>60 registros verificados em 5 amostras, 3 desvios. 3 conforme na amostra, 1 desvio isolado: ampliar a amostra, 1 desvio repetido: não conformidade, 0 amostra incompleta</v>
+        <f aca="false">SUM(K14:K18)&amp;" registros verificados em "&amp;COUNTA(C14:C18)&amp;" amostras, "&amp;SUM(L14:L18)&amp;" desvios. "&amp;COUNTIF(N14:N18,"Conforme na amostra")&amp;" conforme na amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio pontual: não conformidade, ampliar a amostra")&amp;" desvio pontual: não conformidade, ampliar a amostra"&amp;", "&amp;COUNTIF(N14:N18,"Desvio repetido: não conformidade")&amp;" desvio repetido: não conformidade"&amp;", "&amp;COUNTIF(N14:N18,"Amostra incompleta")&amp;" amostra incompleta"</f>
+        <v>60 registros verificados em 5 amostras, 3 desvios. 3 conforme na amostra, 1 desvio pontual: não conformidade, ampliar a amostra, 1 desvio repetido: não conformidade, 0 amostra incompleta</v>
       </c>
       <c r="F53" s="21"/>
       <c r="G53" s="21"/>
@@ -9450,7 +9489,7 @@
       <c r="D54" s="20"/>
       <c r="E54" s="21" t="str">
         <f aca="false">COUNTIF(K22:L29,"Conforme")&amp;" conforme"&amp;", "&amp;COUNTIF(K22:L29,"Não conformidade")&amp;" não conformidade"&amp;", "&amp;COUNTIF(K22:L29,"Oportunidade de melhoria")&amp;" oportunidade de melhoria"&amp;". Força: "&amp;COUNTIF(M22:M29,"Forte")&amp;" forte"&amp;", "&amp;COUNTIF(M22:M29,"Média")&amp;" média"&amp;", "&amp;COUNTIF(M22:M29,"Fraca")&amp;" fraca"</f>
-        <v>5 conforme, 2 não conformidade, 1 oportunidade de melhoria. Força: 7 forte, 0 média, 1 fraca</v>
+        <v>5 conforme, 3 não conformidade, 0 oportunidade de melhoria. Força: 7 forte, 0 média, 1 fraca</v>
       </c>
       <c r="F54" s="21"/>
       <c r="G54" s="21"/>
@@ -9582,7 +9621,7 @@
       <formula>N14="Conforme na amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>N14="Desvio isolado: ampliar a amostra"</formula>
+      <formula>N14="Desvio pontual: não conformidade, ampliar a amostra"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>N14="Amostra incompleta"</formula>
@@ -9626,7 +9665,7 @@
       <formula>$N22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>$N22="Não conformidade sem corroboração"</formula>
+      <formula>$N22="Não conformidade sem evidência objetiva"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>LEN($N22)&gt;0</formula>

--- a/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
+++ b/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
@@ -1787,11 +1787,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="45500717"/>
-        <c:axId val="21500126"/>
+        <c:axId val="67324241"/>
+        <c:axId val="37719046"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45500717"/>
+        <c:axId val="67324241"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1823,7 +1823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21500126"/>
+        <c:crossAx val="37719046"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1831,7 +1831,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21500126"/>
+        <c:axId val="37719046"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1871,7 +1871,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45500717"/>
+        <c:crossAx val="67324241"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
+++ b/Tecnica-Auditoria/Tecnica-Auditoria-modelo.xlsx
@@ -1787,11 +1787,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="67324241"/>
-        <c:axId val="37719046"/>
+        <c:axId val="41699076"/>
+        <c:axId val="81468372"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67324241"/>
+        <c:axId val="41699076"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1823,7 +1823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37719046"/>
+        <c:crossAx val="81468372"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1831,7 +1831,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37719046"/>
+        <c:axId val="81468372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1871,7 +1871,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67324241"/>
+        <c:crossAx val="41699076"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
